--- a/BART_AUTHOR_YEAR_PathwayName_Template.xlsx
+++ b/BART_AUTHOR_YEAR_PathwayName_Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uzh-my.sharepoint.com/personal/stephanie_rich_chem_uzh_ch/Documents/Documents/enviPath-PFAS/BART/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\strich\Documents\BART\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{5782AB4B-F8D2-4D07-B37F-99B812C57055}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{818640DB-F60F-4168-B90F-58312BDE4573}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C740C756-E983-420D-A754-0381759E8C3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{A95DC0BB-2293-4BB2-9652-B6AD234FE081}"/>
+    <workbookView xWindow="-28920" yWindow="1605" windowWidth="29040" windowHeight="16440" firstSheet="1" activeTab="1" xr2:uid="{A95DC0BB-2293-4BB2-9652-B6AD234FE081}"/>
   </bookViews>
   <sheets>
     <sheet name="Description" sheetId="15" r:id="rId1"/>
@@ -101,7 +101,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="763" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="769" uniqueCount="165">
   <si>
     <t>pH</t>
   </si>
@@ -160,15 +160,9 @@
     <t>Initial amount of sludge in bioreactor</t>
   </si>
   <si>
-    <t>Product</t>
-  </si>
-  <si>
     <t>Reactant_SMILES</t>
   </si>
   <si>
-    <t>Product_SMILES</t>
-  </si>
-  <si>
     <t>Biological treatment technology</t>
   </si>
   <si>
@@ -578,6 +572,30 @@
   </si>
   <si>
     <t>Not specified</t>
+  </si>
+  <si>
+    <t>Alternative structure 1</t>
+  </si>
+  <si>
+    <t>Alternative structure 2</t>
+  </si>
+  <si>
+    <t>Alternative structure 3</t>
+  </si>
+  <si>
+    <t>Product 1</t>
+  </si>
+  <si>
+    <t>Product 2</t>
+  </si>
+  <si>
+    <t>Product 1_SMILES</t>
+  </si>
+  <si>
+    <t>Product 2_SMILES</t>
+  </si>
+  <si>
+    <t>Transformation Description</t>
   </si>
 </sst>
 </file>
@@ -963,6 +981,9 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -977,9 +998,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1945,47 +1963,47 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="85.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="15" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B2" s="16"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="17" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B3" s="18"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B5" s="20"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B6" s="20"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="21" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B7" s="22"/>
     </row>
@@ -2005,18 +2023,18 @@
   <sheetPr>
     <tabColor rgb="FFC00000"/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.21875" customWidth="1"/>
     <col min="2" max="2" width="21.21875" customWidth="1"/>
-    <col min="3" max="3" width="126.44140625" customWidth="1"/>
-    <col min="4" max="4" width="12.6640625" customWidth="1"/>
-    <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="18.6640625" customWidth="1"/>
+    <col min="3" max="3" width="47.21875" customWidth="1"/>
+    <col min="4" max="4" width="20.88671875" customWidth="1"/>
+    <col min="5" max="5" width="22.6640625" customWidth="1"/>
+    <col min="6" max="6" width="24.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
         <v>10</v>
       </c>
@@ -2026,98 +2044,107 @@
       <c r="C1" s="5" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D1" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="4"/>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="13"/>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>11</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="13"/>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="13"/>
     </row>
-    <row r="6" spans="1:3" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>11</v>
       </c>
       <c r="B6" s="1"/>
     </row>
-    <row r="7" spans="1:3" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>11</v>
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="13"/>
     </row>
-    <row r="8" spans="1:3" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>11</v>
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="13"/>
     </row>
-    <row r="9" spans="1:3" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>11</v>
       </c>
       <c r="B9" s="1"/>
     </row>
-    <row r="10" spans="1:3" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>11</v>
       </c>
       <c r="B10" s="1"/>
     </row>
-    <row r="11" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>11</v>
       </c>
       <c r="B11" s="1"/>
     </row>
-    <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>11</v>
       </c>
       <c r="B12" s="1"/>
     </row>
-    <row r="13" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>11</v>
       </c>
       <c r="B13" s="1"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>11</v>
       </c>
       <c r="B14" s="1"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>11</v>
       </c>
       <c r="B15" s="1"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>11</v>
       </c>
@@ -2160,39 +2187,51 @@
   <sheetPr>
     <tabColor rgb="FFC00000"/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.77734375" customWidth="1"/>
     <col min="2" max="2" width="73.77734375" customWidth="1"/>
     <col min="3" max="3" width="19.109375" customWidth="1"/>
     <col min="4" max="4" width="72.6640625" customWidth="1"/>
-    <col min="5" max="5" width="17.109375" customWidth="1"/>
-    <col min="6" max="6" width="17.88671875" customWidth="1"/>
-    <col min="9" max="9" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="19.109375" customWidth="1"/>
+    <col min="6" max="6" width="72.6640625" customWidth="1"/>
+    <col min="7" max="7" width="17.109375" customWidth="1"/>
+    <col min="8" max="8" width="30.5546875" customWidth="1"/>
+    <col min="9" max="9" width="12.77734375" customWidth="1"/>
+    <col min="11" max="11" width="15.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>8</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>19</v>
+        <v>160</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>21</v>
+        <v>162</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>37</v>
+        <v>161</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+        <v>163</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="10"/>
       <c r="B2">
         <f>_xlfn.XLOOKUP(A2,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
@@ -2204,8 +2243,13 @@
         <v>0</v>
       </c>
       <c r="E2" s="10"/>
-    </row>
-    <row r="3" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F2">
+        <f>_xlfn.XLOOKUP(E2,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="10"/>
+    </row>
+    <row r="3" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="10"/>
       <c r="B3">
         <f>_xlfn.XLOOKUP(A3,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
@@ -2217,8 +2261,13 @@
         <v>0</v>
       </c>
       <c r="E3" s="10"/>
-    </row>
-    <row r="4" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F3">
+        <f>_xlfn.XLOOKUP(E3,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <v>0</v>
+      </c>
+      <c r="G3" s="10"/>
+    </row>
+    <row r="4" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="10"/>
       <c r="B4">
         <f>_xlfn.XLOOKUP(A4,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
@@ -2230,8 +2279,13 @@
         <v>0</v>
       </c>
       <c r="E4" s="10"/>
-    </row>
-    <row r="5" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F4">
+        <f>_xlfn.XLOOKUP(E4,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <v>0</v>
+      </c>
+      <c r="G4" s="10"/>
+    </row>
+    <row r="5" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="10"/>
       <c r="B5">
         <f>_xlfn.XLOOKUP(A5,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
@@ -2243,8 +2297,13 @@
         <v>0</v>
       </c>
       <c r="E5" s="10"/>
-    </row>
-    <row r="6" spans="1:6" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F5">
+        <f>_xlfn.XLOOKUP(E5,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="10"/>
+    </row>
+    <row r="6" spans="1:9" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="9"/>
       <c r="B6">
         <f>_xlfn.XLOOKUP(A6,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
@@ -2255,9 +2314,14 @@
         <f>_xlfn.XLOOKUP(C6,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>0</v>
       </c>
-      <c r="E6" s="10"/>
-    </row>
-    <row r="7" spans="1:6" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E6" s="9"/>
+      <c r="F6">
+        <f>_xlfn.XLOOKUP(E6,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="10"/>
+    </row>
+    <row r="7" spans="1:9" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="9"/>
       <c r="B7">
         <f>_xlfn.XLOOKUP(A7,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
@@ -2268,9 +2332,14 @@
         <f>_xlfn.XLOOKUP(C7,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>0</v>
       </c>
-      <c r="E7" s="10"/>
-    </row>
-    <row r="8" spans="1:6" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E7" s="9"/>
+      <c r="F7">
+        <f>_xlfn.XLOOKUP(E7,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="10"/>
+    </row>
+    <row r="8" spans="1:9" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="9"/>
       <c r="B8">
         <f>_xlfn.XLOOKUP(A8,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
@@ -2281,9 +2350,14 @@
         <f>_xlfn.XLOOKUP(C8,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>0</v>
       </c>
-      <c r="E8" s="10"/>
-    </row>
-    <row r="9" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E8" s="9"/>
+      <c r="F8">
+        <f>_xlfn.XLOOKUP(E8,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="10"/>
+    </row>
+    <row r="9" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="10"/>
       <c r="B9">
         <f>_xlfn.XLOOKUP(A9,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
@@ -2295,8 +2369,13 @@
         <v>0</v>
       </c>
       <c r="E9" s="10"/>
-    </row>
-    <row r="10" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F9">
+        <f>_xlfn.XLOOKUP(E9,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="10"/>
+    </row>
+    <row r="10" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="10"/>
       <c r="B10">
         <f>_xlfn.XLOOKUP(A10,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
@@ -2308,8 +2387,13 @@
         <v>0</v>
       </c>
       <c r="E10" s="10"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F10">
+        <f>_xlfn.XLOOKUP(E10,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="10"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="9"/>
       <c r="B11">
         <f>_xlfn.XLOOKUP(A11,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
@@ -2320,9 +2404,14 @@
         <f>_xlfn.XLOOKUP(C11,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>0</v>
       </c>
-      <c r="E11" s="10"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E11" s="9"/>
+      <c r="F11">
+        <f>_xlfn.XLOOKUP(E11,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="10"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="9"/>
       <c r="B12">
         <f>_xlfn.XLOOKUP(A12,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
@@ -2333,9 +2422,14 @@
         <f>_xlfn.XLOOKUP(C12,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>0</v>
       </c>
-      <c r="E12" s="10"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E12" s="9"/>
+      <c r="F12">
+        <f>_xlfn.XLOOKUP(E12,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="10"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="9"/>
       <c r="B13">
         <f>_xlfn.XLOOKUP(A13,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
@@ -2346,9 +2440,14 @@
         <f>_xlfn.XLOOKUP(C13,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>0</v>
       </c>
-      <c r="E13" s="10"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E13" s="9"/>
+      <c r="F13">
+        <f>_xlfn.XLOOKUP(E13,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="10"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="9"/>
       <c r="B14">
         <f>_xlfn.XLOOKUP(A14,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
@@ -2359,9 +2458,14 @@
         <f>_xlfn.XLOOKUP(C14,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>0</v>
       </c>
-      <c r="E14" s="10"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E14" s="9"/>
+      <c r="F14">
+        <f>_xlfn.XLOOKUP(E14,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="10"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="9"/>
       <c r="B15">
         <f>_xlfn.XLOOKUP(A15,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
@@ -2372,9 +2476,14 @@
         <f>_xlfn.XLOOKUP(C15,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>0</v>
       </c>
-      <c r="E15" s="10"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E15" s="9"/>
+      <c r="F15">
+        <f>_xlfn.XLOOKUP(E15,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <v>0</v>
+      </c>
+      <c r="G15" s="10"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="9"/>
       <c r="B16">
         <f>_xlfn.XLOOKUP(A16,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
@@ -2385,9 +2494,14 @@
         <f>_xlfn.XLOOKUP(C16,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>0</v>
       </c>
-      <c r="E16" s="10"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E16" s="9"/>
+      <c r="F16">
+        <f>_xlfn.XLOOKUP(E16,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <v>0</v>
+      </c>
+      <c r="G16" s="10"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="9"/>
       <c r="B17">
         <f>_xlfn.XLOOKUP(A17,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
@@ -2398,9 +2512,14 @@
         <f>_xlfn.XLOOKUP(C17,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>0</v>
       </c>
-      <c r="E17" s="10"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E17" s="9"/>
+      <c r="F17">
+        <f>_xlfn.XLOOKUP(E17,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <v>0</v>
+      </c>
+      <c r="G17" s="10"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="9"/>
       <c r="B18">
         <f>_xlfn.XLOOKUP(A18,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
@@ -2411,9 +2530,14 @@
         <f>_xlfn.XLOOKUP(C18,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>0</v>
       </c>
-      <c r="E18" s="10"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E18" s="9"/>
+      <c r="F18">
+        <f>_xlfn.XLOOKUP(E18,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <v>0</v>
+      </c>
+      <c r="G18" s="10"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="9"/>
       <c r="B19">
         <f>_xlfn.XLOOKUP(A19,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
@@ -2424,9 +2548,14 @@
         <f>_xlfn.XLOOKUP(C19,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>0</v>
       </c>
-      <c r="E19" s="10"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E19" s="9"/>
+      <c r="F19">
+        <f>_xlfn.XLOOKUP(E19,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <v>0</v>
+      </c>
+      <c r="G19" s="10"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="9"/>
       <c r="B20">
         <f>_xlfn.XLOOKUP(A20,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
@@ -2437,9 +2566,14 @@
         <f>_xlfn.XLOOKUP(C20,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>0</v>
       </c>
-      <c r="E20" s="10"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E20" s="9"/>
+      <c r="F20">
+        <f>_xlfn.XLOOKUP(E20,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <v>0</v>
+      </c>
+      <c r="G20" s="10"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="9"/>
       <c r="B21">
         <f>_xlfn.XLOOKUP(A21,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
@@ -2450,9 +2584,14 @@
         <f>_xlfn.XLOOKUP(C21,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>0</v>
       </c>
-      <c r="E21" s="10"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E21" s="9"/>
+      <c r="F21">
+        <f>_xlfn.XLOOKUP(E21,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <v>0</v>
+      </c>
+      <c r="G21" s="10"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="9"/>
       <c r="B22">
         <f>_xlfn.XLOOKUP(A22,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
@@ -2463,9 +2602,14 @@
         <f>_xlfn.XLOOKUP(C22,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>0</v>
       </c>
-      <c r="E22" s="10"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E22" s="9"/>
+      <c r="F22">
+        <f>_xlfn.XLOOKUP(E22,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <v>0</v>
+      </c>
+      <c r="G22" s="10"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="9"/>
       <c r="B23">
         <f>_xlfn.XLOOKUP(A23,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
@@ -2476,31 +2620,39 @@
         <f>_xlfn.XLOOKUP(C23,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>0</v>
       </c>
-      <c r="E23" s="10"/>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E23" s="9"/>
+      <c r="F23">
+        <f>_xlfn.XLOOKUP(E23,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <v>0</v>
+      </c>
+      <c r="G23" s="10"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="9"/>
       <c r="C24" s="9"/>
-      <c r="E24" s="10"/>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E24" s="9"/>
+      <c r="G24" s="10"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="9"/>
       <c r="C25" s="9"/>
-      <c r="E25" s="10"/>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E25" s="9"/>
+      <c r="G25" s="10"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="9"/>
       <c r="C26" s="9"/>
-      <c r="E26" s="10"/>
+      <c r="E26" s="9"/>
+      <c r="G26" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E26" xr:uid="{4E4B432C-3A87-4B1A-A0B5-DE103EF115B8}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G26" xr:uid="{4E4B432C-3A87-4B1A-A0B5-DE103EF115B8}">
       <formula1>"multistep reaction, "</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Multistep" prompt="If the reported reaction consisted of multiple enzymatic steps, please note this here by choosing &quot;multistep reaction&quot;" sqref="E1" xr:uid="{670B067C-E023-4CDC-B74A-A2B35314F74C}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Comment" prompt="Use this column to take note of confusing entries or data that shoudl be included in future versions of this template." sqref="F1" xr:uid="{CB5F148A-FFF9-4AAA-8D3A-53806F4B9DE0}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Multistep" prompt="If the reported reaction consisted of multiple enzymatic steps, please note this here by choosing &quot;multistep reaction&quot;" sqref="G1" xr:uid="{670B067C-E023-4CDC-B74A-A2B35314F74C}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Comment" prompt="Use this column to take note of confusing entries or data that shoudl be included in future versions of this template." sqref="I1" xr:uid="{CB5F148A-FFF9-4AAA-8D3A-53806F4B9DE0}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2511,7 +2663,7 @@
           <x14:formula1>
             <xm:f>Compounds!$B$2:$B$21</xm:f>
           </x14:formula1>
-          <xm:sqref>C2:C26 A2:A26</xm:sqref>
+          <xm:sqref>C2:C26 A2:A26 E2:E26</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2542,13 +2694,13 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>2</v>
@@ -2560,13 +2712,13 @@
         <v>3</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2574,13 +2726,13 @@
         <v>9</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="C2" s="54" t="s">
-        <v>137</v>
+        <v>155</v>
+      </c>
+      <c r="C2" s="55" t="s">
+        <v>135</v>
       </c>
       <c r="D2" s="39" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E2" s="40"/>
       <c r="F2" s="31"/>
@@ -2590,12 +2742,12 @@
     </row>
     <row r="3" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="C3" s="55"/>
+        <v>152</v>
+      </c>
+      <c r="C3" s="56"/>
       <c r="D3" s="26" t="s">
         <v>14</v>
       </c>
@@ -2606,9 +2758,9 @@
       <c r="I3" s="29"/>
     </row>
     <row r="4" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="55"/>
+      <c r="C4" s="56"/>
       <c r="D4" s="26" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E4" s="27"/>
       <c r="F4" s="30"/>
@@ -2617,9 +2769,9 @@
       <c r="I4" s="29"/>
     </row>
     <row r="5" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C5" s="55"/>
+      <c r="C5" s="56"/>
       <c r="D5" s="26" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E5" s="27"/>
       <c r="F5" s="28"/>
@@ -2628,21 +2780,21 @@
       <c r="I5" s="29"/>
     </row>
     <row r="6" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C6" s="56"/>
+      <c r="C6" s="57"/>
       <c r="D6" s="26" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E6" s="32"/>
       <c r="F6" s="28"/>
       <c r="G6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H6" s="44"/>
       <c r="I6" s="29"/>
     </row>
     <row r="7" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C7" s="54" t="s">
-        <v>138</v>
+      <c r="C7" s="55" t="s">
+        <v>136</v>
       </c>
       <c r="D7" s="39" t="s">
         <v>13</v>
@@ -2650,26 +2802,26 @@
       <c r="E7" s="41"/>
       <c r="F7" s="41"/>
       <c r="G7" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H7" s="42"/>
       <c r="I7" s="29"/>
     </row>
     <row r="8" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C8" s="55"/>
+      <c r="C8" s="56"/>
       <c r="D8" s="26" t="s">
         <v>18</v>
       </c>
       <c r="E8" s="27"/>
       <c r="F8" s="28"/>
       <c r="G8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H8" s="44"/>
       <c r="I8" s="29"/>
     </row>
     <row r="9" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="55"/>
+      <c r="C9" s="56"/>
       <c r="D9" s="26" t="s">
         <v>12</v>
       </c>
@@ -2680,9 +2832,9 @@
       <c r="I9" s="29"/>
     </row>
     <row r="10" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C10" s="55"/>
+      <c r="C10" s="56"/>
       <c r="D10" s="26" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E10" s="27"/>
       <c r="F10" s="28"/>
@@ -2691,148 +2843,148 @@
       <c r="I10" s="29"/>
     </row>
     <row r="11" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C11" s="55"/>
+      <c r="C11" s="56"/>
       <c r="D11" s="26" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E11" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F11" s="28"/>
       <c r="G11" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H11" s="29" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I11" s="29"/>
     </row>
     <row r="12" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C12" s="55"/>
+      <c r="C12" s="56"/>
       <c r="D12" s="26" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E12" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F12" s="28"/>
       <c r="G12" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H12" s="29" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I12" s="29"/>
     </row>
     <row r="13" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C13" s="55"/>
+      <c r="C13" s="56"/>
       <c r="D13" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="E13" t="s">
         <v>103</v>
-      </c>
-      <c r="E13" t="s">
-        <v>105</v>
       </c>
       <c r="F13" s="28"/>
       <c r="G13" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H13" s="29" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I13" s="29"/>
     </row>
     <row r="14" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C14" s="55"/>
+      <c r="C14" s="56"/>
       <c r="D14" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="E14" t="s">
         <v>103</v>
-      </c>
-      <c r="E14" t="s">
-        <v>105</v>
       </c>
       <c r="F14" s="28"/>
       <c r="G14" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H14" s="29" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I14" s="29"/>
     </row>
     <row r="15" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C15" s="55"/>
+      <c r="C15" s="56"/>
       <c r="D15" s="26" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E15" s="27"/>
       <c r="F15" s="28"/>
       <c r="G15" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H15" s="44"/>
       <c r="I15" s="29"/>
     </row>
     <row r="16" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C16" s="55"/>
+      <c r="C16" s="56"/>
       <c r="D16" s="26" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E16" s="27"/>
       <c r="F16" s="28"/>
       <c r="G16" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H16" s="29" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="I16" s="29"/>
     </row>
     <row r="17" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C17" s="55"/>
+      <c r="C17" s="56"/>
       <c r="D17" s="26" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E17" s="27"/>
       <c r="F17" s="28"/>
       <c r="G17" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H17" s="29" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I17" s="29"/>
     </row>
     <row r="18" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C18" s="55"/>
+      <c r="C18" s="56"/>
       <c r="D18" s="26" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E18" s="27"/>
       <c r="F18" s="28"/>
       <c r="G18" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H18" s="29" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="I18" s="29"/>
     </row>
     <row r="19" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C19" s="55"/>
+      <c r="C19" s="56"/>
       <c r="D19" s="26" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E19" s="27"/>
       <c r="F19" s="28"/>
       <c r="G19" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H19" s="29" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I19" s="29"/>
     </row>
     <row r="20" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C20" s="55"/>
+      <c r="C20" s="56"/>
       <c r="D20" s="26" t="s">
         <v>1</v>
       </c>
@@ -2843,7 +2995,7 @@
       <c r="I20" s="29"/>
     </row>
     <row r="21" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C21" s="55"/>
+      <c r="C21" s="56"/>
       <c r="D21" s="26" t="s">
         <v>16</v>
       </c>
@@ -2854,159 +3006,159 @@
       <c r="I21" s="29"/>
     </row>
     <row r="22" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C22" s="55"/>
+      <c r="C22" s="56"/>
       <c r="D22" s="26" t="s">
         <v>6</v>
       </c>
       <c r="E22" s="27"/>
       <c r="F22" s="28"/>
       <c r="G22" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H22" s="29" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I22" s="29"/>
     </row>
     <row r="23" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C23" s="55"/>
+      <c r="C23" s="56"/>
       <c r="D23" s="26" t="s">
         <v>6</v>
       </c>
       <c r="E23" s="27"/>
       <c r="F23" s="28"/>
       <c r="G23" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H23" s="29" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I23" s="29"/>
     </row>
     <row r="24" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C24" s="55"/>
+      <c r="C24" s="56"/>
       <c r="D24" s="26" t="s">
         <v>0</v>
       </c>
       <c r="E24" s="30"/>
       <c r="F24" s="28"/>
       <c r="G24" s="27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H24" s="29" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I24" s="29"/>
     </row>
     <row r="25" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C25" s="55"/>
+      <c r="C25" s="56"/>
       <c r="D25" s="26" t="s">
         <v>0</v>
       </c>
       <c r="E25" s="30"/>
       <c r="F25" s="28"/>
       <c r="G25" s="27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H25" s="29" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I25" s="29"/>
     </row>
     <row r="26" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C26" s="55"/>
+      <c r="C26" s="56"/>
       <c r="D26" s="26" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E26" s="32"/>
       <c r="F26" s="28"/>
       <c r="G26" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H26" s="29" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I26" s="29"/>
     </row>
     <row r="27" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C27" s="55"/>
+      <c r="C27" s="56"/>
       <c r="D27" s="26" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E27" s="32"/>
       <c r="F27" s="28"/>
       <c r="G27" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H27" s="29" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I27" s="29"/>
     </row>
     <row r="28" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C28" s="55"/>
+      <c r="C28" s="56"/>
       <c r="D28" s="26" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E28" s="32"/>
       <c r="F28" s="28"/>
       <c r="G28" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H28" s="29" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I28" s="29"/>
     </row>
     <row r="29" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C29" s="55"/>
+      <c r="C29" s="56"/>
       <c r="D29" s="26" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E29" s="32"/>
       <c r="F29" s="28"/>
       <c r="G29" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H29" s="29" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I29" s="29"/>
     </row>
     <row r="30" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C30" s="55"/>
+      <c r="C30" s="56"/>
       <c r="D30" s="26" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E30" s="27"/>
       <c r="F30" s="28"/>
       <c r="G30" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H30" s="29" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I30" s="29"/>
     </row>
     <row r="31" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C31" s="55"/>
+      <c r="C31" s="56"/>
       <c r="D31" s="26" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E31" s="27"/>
       <c r="F31" s="28"/>
       <c r="G31" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H31" s="29" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I31" s="29"/>
     </row>
     <row r="32" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C32" s="55"/>
+      <c r="C32" s="56"/>
       <c r="D32" s="26" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E32" s="27"/>
       <c r="F32" s="28"/>
@@ -3015,99 +3167,99 @@
       <c r="I32" s="29"/>
     </row>
     <row r="33" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C33" s="55"/>
+      <c r="C33" s="56"/>
       <c r="D33" s="26" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E33" s="27"/>
       <c r="F33" s="28"/>
       <c r="G33" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H33" s="29" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="I33" s="29"/>
     </row>
     <row r="34" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C34" s="55"/>
+      <c r="C34" s="56"/>
       <c r="D34" s="26" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E34" s="27"/>
       <c r="F34" s="28"/>
       <c r="G34" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H34" s="29" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I34" s="29"/>
     </row>
     <row r="35" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C35" s="55"/>
+      <c r="C35" s="56"/>
       <c r="D35" s="26" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E35" s="27"/>
       <c r="F35" s="28"/>
       <c r="G35" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H35" s="29" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="I35" s="29"/>
     </row>
     <row r="36" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C36" s="55"/>
+      <c r="C36" s="56"/>
       <c r="D36" s="26" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E36" s="27"/>
       <c r="F36" s="28"/>
       <c r="G36" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H36" s="29" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I36" s="29"/>
     </row>
     <row r="37" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C37" s="55"/>
+      <c r="C37" s="56"/>
       <c r="D37" s="26" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E37" s="27"/>
       <c r="F37" s="28"/>
       <c r="G37" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H37" s="29" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I37" s="29"/>
     </row>
     <row r="38" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C38" s="55"/>
+      <c r="C38" s="56"/>
       <c r="D38" s="26" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E38" s="27"/>
       <c r="F38" s="28"/>
       <c r="G38" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H38" s="29" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I38" s="29"/>
     </row>
     <row r="39" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C39" s="56"/>
+      <c r="C39" s="57"/>
       <c r="D39" s="26" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E39" s="27"/>
       <c r="F39" s="30"/>
@@ -3116,22 +3268,22 @@
       <c r="I39" s="29"/>
     </row>
     <row r="40" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C40" s="54" t="s">
-        <v>140</v>
+      <c r="C40" s="55" t="s">
+        <v>138</v>
       </c>
       <c r="D40" s="39" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E40" s="40"/>
       <c r="F40" s="41"/>
       <c r="G40" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H40" s="42"/>
       <c r="I40" s="43"/>
     </row>
     <row r="41" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C41" s="55"/>
+      <c r="C41" s="56"/>
       <c r="D41" s="26" t="s">
         <v>17</v>
       </c>
@@ -3142,12 +3294,12 @@
       <c r="I41" s="29"/>
     </row>
     <row r="42" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C42" s="55"/>
+      <c r="C42" s="56"/>
       <c r="D42" s="26" t="s">
         <v>15</v>
       </c>
       <c r="E42" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F42" s="30"/>
       <c r="G42" s="27"/>
@@ -3155,12 +3307,12 @@
       <c r="I42" s="29"/>
     </row>
     <row r="43" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C43" s="55"/>
+      <c r="C43" s="56"/>
       <c r="D43" s="26" t="s">
         <v>15</v>
       </c>
       <c r="E43" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F43" s="30"/>
       <c r="G43" s="27"/>
@@ -3168,12 +3320,12 @@
       <c r="I43" s="29"/>
     </row>
     <row r="44" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C44" s="56"/>
+      <c r="C44" s="57"/>
       <c r="D44" s="26" t="s">
         <v>15</v>
       </c>
       <c r="E44" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F44" s="30"/>
       <c r="G44" s="27"/>
@@ -3181,11 +3333,11 @@
       <c r="I44" s="29"/>
     </row>
     <row r="45" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C45" s="54" t="s">
-        <v>141</v>
+      <c r="C45" s="55" t="s">
+        <v>139</v>
       </c>
       <c r="D45" s="39" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>9</v>
@@ -3196,12 +3348,12 @@
       <c r="I45" s="43"/>
     </row>
     <row r="46" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C46" s="55"/>
+      <c r="C46" s="56"/>
       <c r="D46" s="26" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E46" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F46" s="28"/>
       <c r="G46" s="27"/>
@@ -3209,9 +3361,9 @@
       <c r="I46" s="29"/>
     </row>
     <row r="47" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C47" s="55"/>
+      <c r="C47" s="56"/>
       <c r="D47" s="26" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E47" s="32"/>
       <c r="F47" s="28"/>
@@ -3220,9 +3372,9 @@
       <c r="I47" s="29"/>
     </row>
     <row r="48" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C48" s="55"/>
+      <c r="C48" s="56"/>
       <c r="D48" s="26" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E48" s="27"/>
       <c r="F48" s="28"/>
@@ -3231,73 +3383,73 @@
       <c r="I48" s="29"/>
     </row>
     <row r="49" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C49" s="55"/>
+      <c r="C49" s="56"/>
       <c r="D49" s="26" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E49" s="27"/>
       <c r="F49" s="28"/>
       <c r="G49" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H49" s="29" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="I49" s="29"/>
     </row>
     <row r="50" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C50" s="55"/>
+      <c r="C50" s="56"/>
       <c r="D50" s="26" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E50" s="27"/>
       <c r="F50" s="28"/>
       <c r="G50" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H50" s="29" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I50" s="29"/>
     </row>
     <row r="51" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C51" s="55"/>
+      <c r="C51" s="56"/>
       <c r="D51" s="26" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E51" s="27"/>
       <c r="F51" s="28"/>
       <c r="G51" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H51" s="29" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="I51" s="29"/>
     </row>
     <row r="52" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C52" s="55"/>
+      <c r="C52" s="56"/>
       <c r="D52" s="26" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E52" s="27"/>
       <c r="F52" s="28"/>
       <c r="G52" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H52" s="29" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I52" s="29"/>
     </row>
     <row r="53" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C53" s="56"/>
+      <c r="C53" s="57"/>
       <c r="D53" s="33" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E53" s="34"/>
       <c r="F53" s="35" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G53" s="34"/>
       <c r="H53" s="45"/>
@@ -3386,13 +3538,13 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C1" s="46" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D1" s="47" t="s">
         <v>2</v>
@@ -3404,13 +3556,13 @@
         <v>3</v>
       </c>
       <c r="G1" s="47" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H1" s="47" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I1" s="48" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3418,13 +3570,13 @@
         <v>9</v>
       </c>
       <c r="B2" s="38" t="s">
-        <v>143</v>
-      </c>
-      <c r="C2" s="54" t="s">
-        <v>144</v>
+        <v>141</v>
+      </c>
+      <c r="C2" s="55" t="s">
+        <v>142</v>
       </c>
       <c r="D2" s="39" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E2" s="40"/>
       <c r="F2" s="41"/>
@@ -3434,14 +3586,14 @@
     </row>
     <row r="3" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B3" s="38" t="s">
-        <v>154</v>
-      </c>
-      <c r="C3" s="55"/>
+        <v>152</v>
+      </c>
+      <c r="C3" s="56"/>
       <c r="D3" s="26" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E3" s="27"/>
       <c r="F3" s="30"/>
@@ -3450,54 +3602,54 @@
       <c r="I3" s="29"/>
     </row>
     <row r="4" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="55"/>
+      <c r="C4" s="56"/>
       <c r="D4" s="26" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F4" s="28"/>
       <c r="G4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H4" s="44"/>
       <c r="I4" s="29"/>
     </row>
     <row r="5" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C5" s="55"/>
+      <c r="C5" s="56"/>
       <c r="D5" s="26" t="s">
+        <v>119</v>
+      </c>
+      <c r="E5" t="s">
         <v>121</v>
-      </c>
-      <c r="E5" t="s">
-        <v>123</v>
       </c>
       <c r="F5" s="28"/>
       <c r="G5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H5" s="44"/>
       <c r="I5" s="29"/>
     </row>
     <row r="6" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C6" s="55"/>
+      <c r="C6" s="56"/>
       <c r="D6" s="26" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F6" s="28"/>
       <c r="G6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H6" s="44"/>
       <c r="I6" s="29"/>
     </row>
     <row r="7" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C7" s="56"/>
+      <c r="C7" s="57"/>
       <c r="D7" s="26" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E7" s="27"/>
       <c r="F7" s="30"/>
@@ -3506,8 +3658,8 @@
       <c r="I7" s="29"/>
     </row>
     <row r="8" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C8" s="54" t="s">
-        <v>145</v>
+      <c r="C8" s="55" t="s">
+        <v>143</v>
       </c>
       <c r="D8" s="39" t="s">
         <v>1</v>
@@ -3519,86 +3671,86 @@
       <c r="I8" s="43"/>
     </row>
     <row r="9" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="55"/>
+      <c r="C9" s="56"/>
       <c r="D9" s="26" t="s">
         <v>0</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="28"/>
       <c r="G9" s="27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H9" s="29" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I9" s="29"/>
       <c r="J9" s="50"/>
     </row>
     <row r="10" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C10" s="55"/>
+      <c r="C10" s="56"/>
       <c r="D10" s="26" t="s">
         <v>0</v>
       </c>
       <c r="E10" s="30"/>
       <c r="F10" s="28"/>
       <c r="G10" s="27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H10" s="29" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I10" s="29"/>
     </row>
     <row r="11" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C11" s="55"/>
+      <c r="C11" s="56"/>
       <c r="D11" s="26" t="s">
         <v>6</v>
       </c>
       <c r="E11" s="27"/>
       <c r="F11" s="28"/>
       <c r="G11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H11" s="29" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I11" s="29"/>
     </row>
     <row r="12" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C12" s="55"/>
+      <c r="C12" s="56"/>
       <c r="D12" s="26" t="s">
         <v>6</v>
       </c>
       <c r="E12" s="27"/>
       <c r="F12" s="28"/>
       <c r="G12" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H12" s="29" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I12" s="29"/>
     </row>
     <row r="13" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C13" s="55"/>
+      <c r="C13" s="56"/>
       <c r="D13" s="26" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E13" s="27"/>
       <c r="F13" s="28"/>
       <c r="G13" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H13" s="44"/>
       <c r="I13" s="29"/>
     </row>
     <row r="14" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C14" s="55"/>
+      <c r="C14" s="56"/>
       <c r="D14" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="E14" t="s">
         <v>80</v>
-      </c>
-      <c r="E14" t="s">
-        <v>82</v>
       </c>
       <c r="F14" s="28"/>
       <c r="G14" s="27"/>
@@ -3606,35 +3758,35 @@
       <c r="I14" s="29"/>
     </row>
     <row r="15" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C15" s="55"/>
+      <c r="C15" s="56"/>
       <c r="D15" s="26" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E15" s="30"/>
       <c r="F15" s="28"/>
       <c r="G15" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="H15" s="51"/>
       <c r="I15" s="29"/>
     </row>
     <row r="16" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C16" s="55"/>
+      <c r="C16" s="56"/>
       <c r="D16" s="26" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E16" s="30"/>
       <c r="F16" s="28"/>
       <c r="G16" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="H16" s="51"/>
       <c r="I16" s="29"/>
     </row>
     <row r="17" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C17" s="55"/>
+      <c r="C17" s="56"/>
       <c r="D17" s="26" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E17" s="27"/>
       <c r="F17" s="28"/>
@@ -3643,135 +3795,135 @@
       <c r="I17" s="29"/>
     </row>
     <row r="18" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C18" s="55"/>
+      <c r="C18" s="56"/>
       <c r="D18" s="26" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E18" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F18" s="28"/>
       <c r="G18" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H18" s="29" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I18" s="29"/>
     </row>
     <row r="19" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C19" s="55"/>
+      <c r="C19" s="56"/>
       <c r="D19" s="26" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E19" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F19" s="28"/>
       <c r="G19" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H19" s="29" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I19" s="29"/>
     </row>
     <row r="20" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C20" s="55"/>
+      <c r="C20" s="56"/>
       <c r="D20" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="E20" t="s">
         <v>103</v>
-      </c>
-      <c r="E20" t="s">
-        <v>105</v>
       </c>
       <c r="F20" s="28"/>
       <c r="G20" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H20" s="29" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I20" s="29"/>
     </row>
     <row r="21" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C21" s="55"/>
+      <c r="C21" s="56"/>
       <c r="D21" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="E21" t="s">
         <v>103</v>
-      </c>
-      <c r="E21" t="s">
-        <v>105</v>
       </c>
       <c r="F21" s="28"/>
       <c r="G21" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H21" s="29" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I21" s="29"/>
     </row>
     <row r="22" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C22" s="55"/>
+      <c r="C22" s="56"/>
       <c r="D22" s="26" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E22" s="27"/>
       <c r="F22" s="28"/>
       <c r="G22" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H22" s="44"/>
       <c r="I22" s="29"/>
     </row>
     <row r="23" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C23" s="55"/>
+      <c r="C23" s="56"/>
       <c r="D23" s="26" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E23" s="27"/>
       <c r="F23" s="28"/>
       <c r="G23" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H23" s="44"/>
       <c r="I23" s="29"/>
     </row>
     <row r="24" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C24" s="55"/>
+      <c r="C24" s="56"/>
       <c r="D24" s="26" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E24" s="27"/>
       <c r="F24" s="28"/>
       <c r="G24" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H24" s="29" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="I24" s="29"/>
     </row>
     <row r="25" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C25" s="56"/>
+      <c r="C25" s="57"/>
       <c r="D25" s="33" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E25" s="34"/>
       <c r="F25" s="52"/>
       <c r="G25" s="53" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H25" s="36" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I25" s="36"/>
     </row>
     <row r="26" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C26" s="54" t="s">
-        <v>146</v>
+      <c r="C26" s="55" t="s">
+        <v>144</v>
       </c>
       <c r="D26" s="39" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>5</v>
@@ -3782,9 +3934,9 @@
       <c r="I26" s="43"/>
     </row>
     <row r="27" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C27" s="56"/>
+      <c r="C27" s="57"/>
       <c r="D27" s="33" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E27" s="34"/>
       <c r="F27" s="52"/>
@@ -3793,11 +3945,11 @@
       <c r="I27" s="36"/>
     </row>
     <row r="28" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C28" s="54" t="s">
-        <v>141</v>
+      <c r="C28" s="55" t="s">
+        <v>139</v>
       </c>
       <c r="D28" s="39" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>9</v>
@@ -3808,12 +3960,12 @@
       <c r="I28" s="43"/>
     </row>
     <row r="29" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C29" s="55"/>
+      <c r="C29" s="56"/>
       <c r="D29" s="26" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E29" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F29" s="28"/>
       <c r="G29" s="27"/>
@@ -3821,9 +3973,9 @@
       <c r="I29" s="29"/>
     </row>
     <row r="30" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C30" s="55"/>
+      <c r="C30" s="56"/>
       <c r="D30" s="26" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E30" s="32"/>
       <c r="F30" s="28"/>
@@ -3832,9 +3984,9 @@
       <c r="I30" s="29"/>
     </row>
     <row r="31" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C31" s="55"/>
+      <c r="C31" s="56"/>
       <c r="D31" s="26" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E31" s="27"/>
       <c r="F31" s="28"/>
@@ -3843,73 +3995,73 @@
       <c r="I31" s="29"/>
     </row>
     <row r="32" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C32" s="55"/>
+      <c r="C32" s="56"/>
       <c r="D32" s="26" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E32" s="27"/>
       <c r="F32" s="28"/>
       <c r="G32" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H32" s="29" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="I32" s="29"/>
     </row>
     <row r="33" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C33" s="55"/>
+      <c r="C33" s="56"/>
       <c r="D33" s="26" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E33" s="27"/>
       <c r="F33" s="28"/>
       <c r="G33" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H33" s="29" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I33" s="29"/>
     </row>
     <row r="34" spans="3:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C34" s="55"/>
+      <c r="C34" s="56"/>
       <c r="D34" s="26" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E34" s="27"/>
       <c r="F34" s="28"/>
       <c r="G34" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H34" s="29" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="I34" s="29"/>
     </row>
     <row r="35" spans="3:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C35" s="55"/>
+      <c r="C35" s="56"/>
       <c r="D35" s="26" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E35" s="27"/>
       <c r="F35" s="28"/>
       <c r="G35" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H35" s="29" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I35" s="29"/>
     </row>
     <row r="36" spans="3:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C36" s="56"/>
+      <c r="C36" s="57"/>
       <c r="D36" s="33" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E36" s="34"/>
       <c r="F36" s="35" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G36" s="34"/>
       <c r="H36" s="45"/>
@@ -3980,13 +4132,13 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C1" s="46" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D1" s="47" t="s">
         <v>2</v>
@@ -3998,13 +4150,13 @@
         <v>3</v>
       </c>
       <c r="G1" s="47" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H1" s="47" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I1" s="48" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -4012,13 +4164,13 @@
         <v>9</v>
       </c>
       <c r="B2" s="38" t="s">
-        <v>149</v>
-      </c>
-      <c r="C2" s="54" t="s">
-        <v>150</v>
+        <v>147</v>
+      </c>
+      <c r="C2" s="55" t="s">
+        <v>148</v>
       </c>
       <c r="D2" s="39" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E2" s="40"/>
       <c r="F2" s="41"/>
@@ -4028,44 +4180,44 @@
     </row>
     <row r="3" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B3" s="38" t="s">
-        <v>154</v>
-      </c>
-      <c r="C3" s="55"/>
+        <v>152</v>
+      </c>
+      <c r="C3" s="56"/>
       <c r="D3" s="26" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E3" s="27"/>
       <c r="F3" s="28"/>
       <c r="G3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H3" s="29" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I3" s="29"/>
     </row>
     <row r="4" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="55"/>
+      <c r="C4" s="56"/>
       <c r="D4" s="26" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E4" s="27"/>
       <c r="F4" s="28"/>
       <c r="G4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H4" s="29" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I4" s="29"/>
     </row>
     <row r="5" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C5" s="55"/>
+      <c r="C5" s="56"/>
       <c r="D5" s="26" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E5" s="40"/>
       <c r="F5" s="28"/>
@@ -4074,9 +4226,9 @@
       <c r="I5" s="29"/>
     </row>
     <row r="6" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C6" s="55"/>
+      <c r="C6" s="56"/>
       <c r="D6" s="26" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E6" s="27"/>
       <c r="F6" s="30"/>
@@ -4085,54 +4237,54 @@
       <c r="I6" s="29"/>
     </row>
     <row r="7" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C7" s="55"/>
+      <c r="C7" s="56"/>
       <c r="D7" s="26" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E7" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F7" s="28"/>
       <c r="G7" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H7" s="44"/>
       <c r="I7" s="29"/>
     </row>
     <row r="8" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C8" s="55"/>
+      <c r="C8" s="56"/>
       <c r="D8" s="26" t="s">
+        <v>119</v>
+      </c>
+      <c r="E8" t="s">
         <v>121</v>
-      </c>
-      <c r="E8" t="s">
-        <v>123</v>
       </c>
       <c r="F8" s="28"/>
       <c r="G8" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H8" s="44"/>
       <c r="I8" s="29"/>
     </row>
     <row r="9" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="55"/>
+      <c r="C9" s="56"/>
       <c r="D9" s="26" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E9" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F9" s="28"/>
       <c r="G9" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H9" s="44"/>
       <c r="I9" s="29"/>
     </row>
     <row r="10" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C10" s="55"/>
+      <c r="C10" s="56"/>
       <c r="D10" s="26" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E10" s="27"/>
       <c r="F10" s="30"/>
@@ -4141,9 +4293,9 @@
       <c r="I10" s="29"/>
     </row>
     <row r="11" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C11" s="56"/>
+      <c r="C11" s="57"/>
       <c r="D11" s="33" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E11" s="34"/>
       <c r="F11" s="52"/>
@@ -4152,280 +4304,280 @@
       <c r="I11" s="36"/>
     </row>
     <row r="12" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C12" s="54" t="s">
-        <v>145</v>
+      <c r="C12" s="55" t="s">
+        <v>143</v>
       </c>
       <c r="D12" s="39" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F12" s="41"/>
       <c r="G12" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H12" s="42"/>
       <c r="I12" s="29"/>
     </row>
     <row r="13" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C13" s="55"/>
+      <c r="C13" s="56"/>
       <c r="D13" s="26" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F13" s="28"/>
       <c r="G13" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H13" s="44"/>
       <c r="I13" s="29"/>
     </row>
     <row r="14" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C14" s="55"/>
+      <c r="C14" s="56"/>
       <c r="D14" s="26" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E14" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F14" s="28"/>
       <c r="G14" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H14" s="29" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I14" s="29"/>
     </row>
     <row r="15" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C15" s="55"/>
+      <c r="C15" s="56"/>
       <c r="D15" s="26" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E15" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F15" s="28"/>
       <c r="G15" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H15" s="29" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I15" s="29"/>
     </row>
     <row r="16" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C16" s="55"/>
+      <c r="C16" s="56"/>
       <c r="D16" s="26" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E16" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F16" s="28"/>
       <c r="G16" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H16" s="29" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I16" s="29"/>
     </row>
     <row r="17" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C17" s="55"/>
+      <c r="C17" s="56"/>
       <c r="D17" s="26" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E17" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F17" s="28"/>
       <c r="G17" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H17" s="29" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I17" s="29"/>
     </row>
     <row r="18" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C18" s="55"/>
+      <c r="C18" s="56"/>
       <c r="D18" s="26" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E18" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F18" s="28"/>
       <c r="G18" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H18" s="29" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I18" s="29"/>
     </row>
     <row r="19" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C19" s="55"/>
+      <c r="C19" s="56"/>
       <c r="D19" s="26" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E19" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F19" s="28"/>
       <c r="G19" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H19" s="29" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I19" s="29"/>
     </row>
     <row r="20" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C20" s="55"/>
+      <c r="C20" s="56"/>
       <c r="D20" s="26" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E20" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F20" s="28"/>
       <c r="G20" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H20" s="29" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I20" s="29"/>
     </row>
     <row r="21" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C21" s="55"/>
+      <c r="C21" s="56"/>
       <c r="D21" s="26" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E21" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F21" s="28"/>
       <c r="G21" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H21" s="29" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I21" s="29"/>
     </row>
     <row r="22" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C22" s="55"/>
+      <c r="C22" s="56"/>
       <c r="D22" s="26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E22" s="30"/>
       <c r="F22" s="28"/>
       <c r="G22" s="27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H22" s="29" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I22" s="29"/>
     </row>
     <row r="23" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C23" s="55"/>
+      <c r="C23" s="56"/>
       <c r="D23" s="26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E23" s="30"/>
       <c r="F23" s="28"/>
       <c r="G23" s="27" t="s">
+        <v>108</v>
+      </c>
+      <c r="H23" s="29" t="s">
+        <v>75</v>
+      </c>
+      <c r="I23" s="29"/>
+    </row>
+    <row r="24" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C24" s="56"/>
+      <c r="D24" s="26" t="s">
         <v>110</v>
-      </c>
-      <c r="H23" s="29" t="s">
-        <v>77</v>
-      </c>
-      <c r="I23" s="29"/>
-    </row>
-    <row r="24" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C24" s="55"/>
-      <c r="D24" s="26" t="s">
-        <v>112</v>
       </c>
       <c r="E24" s="30"/>
       <c r="F24" s="28"/>
       <c r="G24" s="27" t="s">
+        <v>108</v>
+      </c>
+      <c r="H24" s="29" t="s">
+        <v>74</v>
+      </c>
+      <c r="I24" s="29"/>
+    </row>
+    <row r="25" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C25" s="56"/>
+      <c r="D25" s="26" t="s">
         <v>110</v>
-      </c>
-      <c r="H24" s="29" t="s">
-        <v>76</v>
-      </c>
-      <c r="I24" s="29"/>
-    </row>
-    <row r="25" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C25" s="55"/>
-      <c r="D25" s="26" t="s">
-        <v>112</v>
       </c>
       <c r="E25" s="30"/>
       <c r="F25" s="28"/>
       <c r="G25" s="27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H25" s="29" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I25" s="29"/>
     </row>
     <row r="26" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C26" s="55"/>
+      <c r="C26" s="56"/>
       <c r="D26" s="26" t="s">
         <v>6</v>
       </c>
       <c r="E26" s="27"/>
       <c r="F26" s="28"/>
       <c r="G26" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H26" s="29" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I26" s="29"/>
     </row>
     <row r="27" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C27" s="55"/>
+      <c r="C27" s="56"/>
       <c r="D27" s="26" t="s">
         <v>6</v>
       </c>
       <c r="E27" s="27"/>
       <c r="F27" s="28"/>
       <c r="G27" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H27" s="29" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I27" s="29"/>
     </row>
     <row r="28" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C28" s="55"/>
+      <c r="C28" s="56"/>
       <c r="D28" s="26" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E28" s="27"/>
       <c r="F28" s="28"/>
       <c r="G28" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H28" s="44"/>
       <c r="I28" s="29"/>
     </row>
     <row r="29" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C29" s="55"/>
+      <c r="C29" s="56"/>
       <c r="D29" s="26" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E29" s="27"/>
       <c r="F29" s="28"/>
@@ -4434,348 +4586,348 @@
       <c r="I29" s="29"/>
     </row>
     <row r="30" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C30" s="55"/>
+      <c r="C30" s="56"/>
       <c r="D30" s="26" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E30" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F30" s="28"/>
       <c r="G30" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H30" s="29" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I30" s="29"/>
     </row>
     <row r="31" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C31" s="55"/>
+      <c r="C31" s="56"/>
       <c r="D31" s="26" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E31" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F31" s="28"/>
       <c r="G31" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H31" s="29" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I31" s="29"/>
     </row>
     <row r="32" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C32" s="55"/>
+      <c r="C32" s="56"/>
       <c r="D32" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="E32" t="s">
         <v>103</v>
-      </c>
-      <c r="E32" t="s">
-        <v>105</v>
       </c>
       <c r="F32" s="28"/>
       <c r="G32" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H32" s="29" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I32" s="29"/>
     </row>
     <row r="33" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C33" s="55"/>
+      <c r="C33" s="56"/>
       <c r="D33" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="E33" t="s">
         <v>103</v>
-      </c>
-      <c r="E33" t="s">
-        <v>105</v>
       </c>
       <c r="F33" s="28"/>
       <c r="G33" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H33" s="29" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I33" s="29"/>
     </row>
     <row r="34" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C34" s="55"/>
+      <c r="C34" s="56"/>
       <c r="D34" s="26" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E34" s="27"/>
       <c r="F34" s="28"/>
       <c r="G34" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H34" s="29" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="I34" s="29"/>
     </row>
     <row r="35" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C35" s="55"/>
+      <c r="C35" s="56"/>
       <c r="D35" s="26" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E35" s="27"/>
       <c r="F35" s="28"/>
       <c r="G35" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H35" s="29" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I35" s="29"/>
     </row>
     <row r="36" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C36" s="55"/>
+      <c r="C36" s="56"/>
       <c r="D36" s="26" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E36" s="27"/>
       <c r="F36" s="28"/>
       <c r="G36" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H36" s="29" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="I36" s="29"/>
     </row>
     <row r="37" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C37" s="55"/>
+      <c r="C37" s="56"/>
       <c r="D37" s="26" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E37" s="27"/>
       <c r="F37" s="28"/>
       <c r="G37" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H37" s="29" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I37" s="29"/>
     </row>
     <row r="38" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C38" s="55"/>
+      <c r="C38" s="56"/>
       <c r="D38" s="26" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E38" s="27"/>
       <c r="F38" s="28"/>
       <c r="G38" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H38" s="29" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="I38" s="29"/>
     </row>
     <row r="39" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C39" s="55"/>
+      <c r="C39" s="56"/>
       <c r="D39" s="26" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E39" s="27"/>
       <c r="F39" s="28"/>
       <c r="G39" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H39" s="29" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I39" s="29"/>
     </row>
     <row r="40" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C40" s="55"/>
+      <c r="C40" s="56"/>
       <c r="D40" s="26" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E40" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F40" s="28"/>
       <c r="G40" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H40" s="29" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I40" s="29"/>
     </row>
     <row r="41" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C41" s="55"/>
+      <c r="C41" s="56"/>
       <c r="D41" s="26" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E41" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F41" s="28"/>
       <c r="G41" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H41" s="29" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I41" s="29"/>
     </row>
     <row r="42" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C42" s="55"/>
+      <c r="C42" s="56"/>
       <c r="D42" s="26" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E42" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F42" s="28"/>
       <c r="G42" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H42" s="29" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I42" s="29"/>
     </row>
     <row r="43" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C43" s="55"/>
+      <c r="C43" s="56"/>
       <c r="D43" s="26" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E43" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F43" s="28"/>
       <c r="G43" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H43" s="29" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I43" s="29"/>
     </row>
     <row r="44" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C44" s="55"/>
+      <c r="C44" s="56"/>
       <c r="D44" s="26" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E44" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F44" s="28"/>
       <c r="G44" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H44" s="29" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I44" s="29"/>
     </row>
     <row r="45" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C45" s="55"/>
+      <c r="C45" s="56"/>
       <c r="D45" s="26" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E45" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F45" s="28"/>
       <c r="G45" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H45" s="29" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I45" s="29"/>
     </row>
     <row r="46" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C46" s="55"/>
+      <c r="C46" s="56"/>
       <c r="D46" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="E46" t="s">
         <v>100</v>
-      </c>
-      <c r="E46" t="s">
-        <v>102</v>
       </c>
       <c r="F46" s="28"/>
       <c r="G46" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H46" s="29" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I46" s="29"/>
     </row>
     <row r="47" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C47" s="55"/>
+      <c r="C47" s="56"/>
       <c r="D47" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="E47" t="s">
         <v>100</v>
-      </c>
-      <c r="E47" t="s">
-        <v>102</v>
       </c>
       <c r="F47" s="28"/>
       <c r="G47" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H47" s="29" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I47" s="29"/>
     </row>
     <row r="48" spans="3:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C48" s="55"/>
+      <c r="C48" s="56"/>
       <c r="D48" s="26" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E48" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F48" s="28"/>
       <c r="G48" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H48" s="44"/>
       <c r="I48" s="29"/>
     </row>
     <row r="49" spans="3:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C49" s="55"/>
+      <c r="C49" s="56"/>
       <c r="D49" s="26" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E49" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F49" s="28"/>
       <c r="G49" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H49" s="44"/>
       <c r="I49" s="29"/>
     </row>
     <row r="50" spans="3:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C50" s="56"/>
+      <c r="C50" s="57"/>
       <c r="D50" s="33" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E50" s="34"/>
       <c r="F50" s="52"/>
       <c r="G50" s="53" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H50" s="45"/>
       <c r="I50" s="36"/>
     </row>
     <row r="51" spans="3:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C51" s="57" t="s">
-        <v>146</v>
+      <c r="C51" s="58" t="s">
+        <v>144</v>
       </c>
       <c r="D51" s="39" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>5</v>
@@ -4786,9 +4938,9 @@
       <c r="I51" s="43"/>
     </row>
     <row r="52" spans="3:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C52" s="58"/>
+      <c r="C52" s="59"/>
       <c r="D52" s="26" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E52" s="27"/>
       <c r="F52" s="28"/>
@@ -4797,11 +4949,11 @@
       <c r="I52" s="29"/>
     </row>
     <row r="53" spans="3:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C53" s="54" t="s">
-        <v>141</v>
+      <c r="C53" s="55" t="s">
+        <v>139</v>
       </c>
       <c r="D53" s="39" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>9</v>
@@ -4812,12 +4964,12 @@
       <c r="I53" s="43"/>
     </row>
     <row r="54" spans="3:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C54" s="55"/>
+      <c r="C54" s="56"/>
       <c r="D54" s="26" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E54" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F54" s="28"/>
       <c r="G54" s="27"/>
@@ -4825,9 +4977,9 @@
       <c r="I54" s="29"/>
     </row>
     <row r="55" spans="3:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C55" s="55"/>
+      <c r="C55" s="56"/>
       <c r="D55" s="26" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E55" s="32"/>
       <c r="F55" s="28"/>
@@ -4836,9 +4988,9 @@
       <c r="I55" s="29"/>
     </row>
     <row r="56" spans="3:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C56" s="55"/>
+      <c r="C56" s="56"/>
       <c r="D56" s="26" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E56" s="27"/>
       <c r="F56" s="28"/>
@@ -4847,73 +4999,73 @@
       <c r="I56" s="29"/>
     </row>
     <row r="57" spans="3:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C57" s="55"/>
+      <c r="C57" s="56"/>
       <c r="D57" s="26" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E57" s="27"/>
       <c r="F57" s="28"/>
       <c r="G57" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H57" s="29" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="I57" s="29"/>
     </row>
     <row r="58" spans="3:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C58" s="55"/>
+      <c r="C58" s="56"/>
       <c r="D58" s="26" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E58" s="27"/>
       <c r="F58" s="28"/>
       <c r="G58" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H58" s="29" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I58" s="29"/>
     </row>
     <row r="59" spans="3:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C59" s="55"/>
+      <c r="C59" s="56"/>
       <c r="D59" s="26" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E59" s="27"/>
       <c r="F59" s="28"/>
       <c r="G59" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H59" s="29" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="I59" s="29"/>
     </row>
     <row r="60" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C60" s="55"/>
+      <c r="C60" s="56"/>
       <c r="D60" s="26" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E60" s="27"/>
       <c r="F60" s="28"/>
       <c r="G60" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H60" s="29" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I60" s="29"/>
     </row>
     <row r="61" spans="3:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C61" s="56"/>
+      <c r="C61" s="57"/>
       <c r="D61" s="33" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E61" s="34"/>
       <c r="F61" s="35" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="G61" s="34"/>
       <c r="H61" s="45"/>
@@ -4976,10 +5128,10 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C1" s="23" t="s">
         <v>2</v>
@@ -4991,13 +5143,13 @@
         <v>3</v>
       </c>
       <c r="F1" s="24" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G1" s="24" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H1" s="25" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -5005,7 +5157,7 @@
         <v>9</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C2" s="26" t="s">
         <v>12</v>
@@ -5018,13 +5170,13 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B3" s="38" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C3" s="26" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D3" s="27"/>
       <c r="E3" s="30"/>
@@ -5034,35 +5186,35 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C4" s="26" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D4" s="27"/>
       <c r="E4" s="28"/>
       <c r="F4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H4" s="29"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C5" s="26" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D5" s="27"/>
       <c r="E5" s="28"/>
       <c r="F5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H5" s="29"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C6" s="26" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D6" s="27"/>
       <c r="E6" s="30"/>
@@ -5077,122 +5229,122 @@
       <c r="D7" s="37"/>
       <c r="E7" s="28"/>
       <c r="F7" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G7" s="27"/>
       <c r="H7" s="29"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C8" s="26" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D8" s="27"/>
       <c r="E8" s="28"/>
       <c r="F8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G8" s="27"/>
       <c r="H8" s="29"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C9" s="26" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D9" s="27"/>
       <c r="E9" s="28"/>
       <c r="F9" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G9" s="27"/>
       <c r="H9" s="29"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C10" s="26" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D10" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E10" s="28"/>
       <c r="F10" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G10" s="27"/>
       <c r="H10" s="29"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C11" s="26" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D11" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E11" s="28"/>
       <c r="F11" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G11" s="27"/>
       <c r="H11" s="29"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C12" s="26" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D12" s="27"/>
       <c r="E12" s="28"/>
       <c r="F12" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G12" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H12" s="29"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C13" s="26" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D13" s="27"/>
       <c r="E13" s="28"/>
       <c r="F13" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G13" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H13" s="29"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C14" s="26" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D14" s="27"/>
       <c r="E14" s="28"/>
       <c r="F14" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G14" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H14" s="29"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C15" s="26" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D15" s="27"/>
       <c r="E15" s="28"/>
       <c r="F15" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G15" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H15" s="29"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C16" s="26" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D16" t="s">
         <v>9</v>
@@ -5204,10 +5356,10 @@
     </row>
     <row r="17" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C17" s="26" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D17" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E17" s="28"/>
       <c r="F17" s="27"/>
@@ -5216,22 +5368,22 @@
     </row>
     <row r="18" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C18" s="26" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D18" s="27"/>
       <c r="E18" s="28"/>
       <c r="F18" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G18" s="27"/>
       <c r="H18" s="29"/>
     </row>
     <row r="19" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C19" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="D19" t="s">
         <v>80</v>
-      </c>
-      <c r="D19" t="s">
-        <v>82</v>
       </c>
       <c r="E19" s="28"/>
       <c r="F19" s="27"/>
@@ -5240,12 +5392,12 @@
     </row>
     <row r="20" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C20" s="26" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D20" s="27"/>
       <c r="E20" s="28"/>
       <c r="F20" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G20" s="27"/>
       <c r="H20" s="29"/>
@@ -5257,54 +5409,54 @@
       <c r="D21" s="27"/>
       <c r="E21" s="28"/>
       <c r="F21" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G21" s="27"/>
       <c r="H21" s="29"/>
     </row>
     <row r="22" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C22" s="26" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D22" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E22" s="28"/>
       <c r="F22" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G22" s="27"/>
       <c r="H22" s="29"/>
     </row>
     <row r="23" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C23" s="26" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D23" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E23" s="28"/>
       <c r="F23" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G23" s="27"/>
       <c r="H23" s="29"/>
     </row>
     <row r="24" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C24" s="26" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D24" s="27"/>
       <c r="E24" s="28"/>
       <c r="F24" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G24" s="27"/>
       <c r="H24" s="29"/>
     </row>
     <row r="25" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C25" s="26" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D25" s="27"/>
       <c r="E25" s="28"/>
@@ -5314,7 +5466,7 @@
     </row>
     <row r="26" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C26" s="26" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D26" s="27"/>
       <c r="E26" s="28"/>
@@ -5324,7 +5476,7 @@
     </row>
     <row r="27" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C27" s="26" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D27" s="27"/>
       <c r="E27" s="31"/>
@@ -5334,275 +5486,275 @@
     </row>
     <row r="28" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C28" s="26" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D28" s="27"/>
       <c r="E28" s="28"/>
       <c r="F28" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G28" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H28" s="29"/>
     </row>
     <row r="29" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C29" s="26" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D29" s="27"/>
       <c r="E29" s="28"/>
       <c r="F29" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G29" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H29" s="29"/>
     </row>
     <row r="30" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C30" s="26" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D30" s="27"/>
       <c r="E30" s="28"/>
       <c r="F30" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G30" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H30" s="29"/>
     </row>
     <row r="31" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C31" s="26" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D31" s="27"/>
       <c r="E31" s="28"/>
       <c r="F31" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G31" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H31" s="29"/>
     </row>
     <row r="32" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C32" s="26" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D32" s="27"/>
       <c r="E32" s="28"/>
       <c r="F32" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G32" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H32" s="29"/>
     </row>
     <row r="33" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C33" s="26" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D33" s="27"/>
       <c r="E33" s="28"/>
       <c r="F33" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G33" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H33" s="29"/>
     </row>
     <row r="34" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C34" s="26" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D34" s="27"/>
       <c r="E34" s="28"/>
       <c r="F34" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G34" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H34" s="29"/>
     </row>
     <row r="35" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C35" s="26" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D35" s="27"/>
       <c r="E35" s="28"/>
       <c r="F35" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G35" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H35" s="29"/>
     </row>
     <row r="36" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C36" s="26" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D36" s="32"/>
       <c r="E36" s="28"/>
       <c r="F36" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G36" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H36" s="29"/>
     </row>
     <row r="37" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C37" s="26" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D37" s="32"/>
       <c r="E37" s="28"/>
       <c r="F37" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G37" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H37" s="29"/>
     </row>
     <row r="38" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C38" s="26" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D38" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E38" s="28"/>
       <c r="F38" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G38" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H38" s="29"/>
     </row>
     <row r="39" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C39" s="26" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D39" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E39" s="28"/>
       <c r="F39" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G39" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H39" s="29"/>
     </row>
     <row r="40" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C40" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="D40" t="s">
         <v>100</v>
-      </c>
-      <c r="D40" t="s">
-        <v>102</v>
       </c>
       <c r="E40" s="28"/>
       <c r="F40" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G40" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H40" s="29"/>
     </row>
     <row r="41" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C41" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="D41" t="s">
         <v>100</v>
-      </c>
-      <c r="D41" t="s">
-        <v>102</v>
       </c>
       <c r="E41" s="28"/>
       <c r="F41" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G41" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H41" s="29"/>
     </row>
     <row r="42" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C42" s="26" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D42" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E42" s="28"/>
       <c r="F42" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G42" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H42" s="29"/>
     </row>
     <row r="43" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C43" s="26" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D43" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E43" s="28"/>
       <c r="F43" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G43" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H43" s="29"/>
     </row>
     <row r="44" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C44" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="D44" t="s">
         <v>103</v>
-      </c>
-      <c r="D44" t="s">
-        <v>105</v>
       </c>
       <c r="E44" s="28"/>
       <c r="F44" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G44" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H44" s="29"/>
     </row>
     <row r="45" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C45" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="D45" t="s">
         <v>103</v>
-      </c>
-      <c r="D45" t="s">
-        <v>105</v>
       </c>
       <c r="E45" s="28"/>
       <c r="F45" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G45" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H45" s="29"/>
     </row>
     <row r="46" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C46" s="26" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D46" s="27"/>
       <c r="E46" s="28"/>
@@ -5612,185 +5764,185 @@
     </row>
     <row r="47" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C47" s="26" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D47" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E47" s="28"/>
       <c r="F47" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G47" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H47" s="29"/>
     </row>
     <row r="48" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C48" s="26" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D48" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E48" s="28"/>
       <c r="F48" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G48" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H48" s="29"/>
     </row>
     <row r="49" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C49" s="26" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D49" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E49" s="28"/>
       <c r="F49" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G49" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H49" s="29"/>
     </row>
     <row r="50" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C50" s="26" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D50" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E50" s="28"/>
       <c r="F50" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G50" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H50" s="29"/>
     </row>
     <row r="51" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C51" s="26" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D51" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E51" s="28"/>
       <c r="F51" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G51" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H51" s="29"/>
     </row>
     <row r="52" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C52" s="26" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D52" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E52" s="28"/>
       <c r="F52" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G52" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H52" s="29"/>
     </row>
     <row r="53" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C53" s="26" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D53" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E53" s="28"/>
       <c r="F53" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G53" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H53" s="29"/>
     </row>
     <row r="54" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C54" s="26" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D54" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E54" s="28"/>
       <c r="F54" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G54" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H54" s="29"/>
     </row>
     <row r="55" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C55" s="26" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D55" s="32"/>
       <c r="E55" s="28"/>
       <c r="F55" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G55" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H55" s="29"/>
     </row>
     <row r="56" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C56" s="26" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D56" s="32"/>
       <c r="E56" s="28"/>
       <c r="F56" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G56" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H56" s="29"/>
     </row>
     <row r="57" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C57" s="26" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D57" s="27"/>
       <c r="E57" s="28"/>
       <c r="F57" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G57" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H57" s="29"/>
     </row>
     <row r="58" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C58" s="26" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D58" s="27"/>
       <c r="E58" s="28"/>
       <c r="F58" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G58" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H58" s="29"/>
     </row>
@@ -5801,10 +5953,10 @@
       <c r="D59" s="30"/>
       <c r="E59" s="28"/>
       <c r="F59" s="27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G59" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H59" s="29"/>
     </row>
@@ -5815,94 +5967,94 @@
       <c r="D60" s="30"/>
       <c r="E60" s="28"/>
       <c r="F60" s="27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G60" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H60" s="29"/>
     </row>
     <row r="61" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C61" s="26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D61" s="30"/>
       <c r="E61" s="28"/>
       <c r="F61" s="27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G61" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H61" s="29"/>
     </row>
     <row r="62" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C62" s="26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D62" s="30"/>
       <c r="E62" s="28"/>
       <c r="F62" s="27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G62" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H62" s="29"/>
     </row>
     <row r="63" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C63" s="26" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D63" s="30"/>
       <c r="E63" s="28"/>
       <c r="F63" s="27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G63" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H63" s="29"/>
     </row>
     <row r="64" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C64" s="26" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D64" s="30"/>
       <c r="E64" s="28"/>
       <c r="F64" s="27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G64" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H64" s="29"/>
     </row>
     <row r="65" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C65" s="26" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D65" s="27"/>
       <c r="E65" s="28"/>
       <c r="F65" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G65" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H65" s="29"/>
     </row>
     <row r="66" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C66" s="26" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D66" s="27"/>
       <c r="E66" s="28"/>
       <c r="F66" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G66" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H66" s="29"/>
     </row>
@@ -5928,71 +6080,71 @@
     </row>
     <row r="69" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C69" s="26" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D69" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E69" s="28"/>
       <c r="F69" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G69" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H69" s="29"/>
     </row>
     <row r="70" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C70" s="26" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D70" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E70" s="28"/>
       <c r="F70" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G70" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H70" s="29"/>
     </row>
     <row r="71" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C71" s="26" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D71" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E71" s="28"/>
       <c r="F71" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G71" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H71" s="29"/>
     </row>
     <row r="72" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C72" s="26" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D72" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E72" s="28"/>
       <c r="F72" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G72" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H72" s="29"/>
     </row>
     <row r="73" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C73" s="26" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D73" s="32"/>
       <c r="E73" s="28"/>
@@ -6002,7 +6154,7 @@
     </row>
     <row r="74" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C74" s="26" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D74" s="27"/>
       <c r="E74" s="28"/>
@@ -6012,35 +6164,35 @@
     </row>
     <row r="75" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C75" s="26" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D75" s="27"/>
       <c r="E75" s="28"/>
       <c r="F75" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G75" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H75" s="29"/>
     </row>
     <row r="76" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C76" s="26" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D76" s="27"/>
       <c r="E76" s="28"/>
       <c r="F76" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G76" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H76" s="29"/>
     </row>
     <row r="77" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C77" s="26" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D77" s="27"/>
       <c r="E77" s="28"/>
@@ -6050,19 +6202,19 @@
     </row>
     <row r="78" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C78" s="26" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D78" s="32"/>
       <c r="E78" s="28"/>
       <c r="F78" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G78" s="27"/>
       <c r="H78" s="29"/>
     </row>
     <row r="79" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C79" s="26" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D79" s="27"/>
       <c r="E79" s="28"/>
@@ -6072,7 +6224,7 @@
     </row>
     <row r="80" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C80" s="26" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="30"/>
@@ -6082,49 +6234,49 @@
     </row>
     <row r="81" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C81" s="26" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D81" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E81" s="28"/>
       <c r="F81" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G81" s="27"/>
       <c r="H81" s="29"/>
     </row>
     <row r="82" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C82" s="26" t="s">
+        <v>119</v>
+      </c>
+      <c r="D82" t="s">
         <v>121</v>
-      </c>
-      <c r="D82" t="s">
-        <v>123</v>
       </c>
       <c r="E82" s="28"/>
       <c r="F82" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G82" s="27"/>
       <c r="H82" s="29"/>
     </row>
     <row r="83" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C83" s="26" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D83" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E83" s="28"/>
       <c r="F83" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G83" s="27"/>
       <c r="H83" s="29"/>
     </row>
     <row r="84" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C84" s="26" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="30"/>
@@ -6137,7 +6289,7 @@
         <v>15</v>
       </c>
       <c r="D85" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E85" s="30"/>
       <c r="F85" s="27"/>
@@ -6149,7 +6301,7 @@
         <v>15</v>
       </c>
       <c r="D86" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E86" s="30"/>
       <c r="F86" s="27"/>
@@ -6161,7 +6313,7 @@
         <v>15</v>
       </c>
       <c r="D87" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E87" s="30"/>
       <c r="F87" s="27"/>
@@ -6170,7 +6322,7 @@
     </row>
     <row r="88" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C88" s="26" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D88" s="27"/>
       <c r="E88" s="28"/>
@@ -6180,19 +6332,19 @@
     </row>
     <row r="89" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C89" s="26" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D89" t="s">
         <v>5</v>
       </c>
-      <c r="E89" s="59"/>
+      <c r="E89" s="54"/>
       <c r="F89" s="27"/>
       <c r="G89" s="27"/>
       <c r="H89" s="29"/>
     </row>
     <row r="90" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C90" s="26" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D90" s="27"/>
       <c r="E90" s="28"/>
@@ -6207,10 +6359,10 @@
       <c r="D91" s="27"/>
       <c r="E91" s="28"/>
       <c r="F91" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G91" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H91" s="29"/>
     </row>
@@ -6221,66 +6373,66 @@
       <c r="D92" s="27"/>
       <c r="E92" s="28"/>
       <c r="F92" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G92" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H92" s="29"/>
     </row>
     <row r="93" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C93" s="26" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D93" s="27"/>
       <c r="E93" s="28"/>
       <c r="F93" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G93" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H93" s="29"/>
     </row>
     <row r="94" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C94" s="26" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D94" s="27"/>
       <c r="E94" s="28"/>
       <c r="F94" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G94" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H94" s="29"/>
     </row>
     <row r="95" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C95" s="26" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D95" s="27"/>
       <c r="E95" s="28"/>
       <c r="F95" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G95" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H95" s="29"/>
     </row>
     <row r="96" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C96" s="26" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D96" s="27"/>
       <c r="E96" s="28"/>
       <c r="F96" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G96" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H96" s="29"/>
     </row>
@@ -6306,63 +6458,63 @@
     </row>
     <row r="99" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C99" s="26" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D99" s="27"/>
       <c r="E99" s="28"/>
       <c r="F99" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G99" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H99" s="29"/>
     </row>
     <row r="100" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C100" s="26" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D100" s="27"/>
       <c r="E100" s="28"/>
       <c r="F100" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G100" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H100" s="29"/>
     </row>
     <row r="101" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C101" s="26" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D101" s="30"/>
       <c r="E101" s="28"/>
       <c r="F101" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G101" s="30"/>
       <c r="H101" s="29"/>
     </row>
     <row r="102" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C102" s="26" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D102" s="30"/>
       <c r="E102" s="28"/>
       <c r="F102" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G102" s="30"/>
       <c r="H102" s="29"/>
     </row>
     <row r="103" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C103" s="33" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D103" s="34"/>
       <c r="E103" s="35" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F103" s="34"/>
       <c r="G103" s="34"/>
@@ -6457,16 +6609,16 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>5</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>2</v>
@@ -6478,22 +6630,22 @@
         <v>4</v>
       </c>
       <c r="H1" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="L1" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="I1" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="L1" s="5" t="s">
-        <v>41</v>
-      </c>
       <c r="M1" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">

--- a/BART_AUTHOR_YEAR_PathwayName_Template.xlsx
+++ b/BART_AUTHOR_YEAR_PathwayName_Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\strich\Documents\BART\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C740C756-E983-420D-A754-0381759E8C3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66A08681-E967-4051-A82D-8A7A686EC45D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1605" windowWidth="29040" windowHeight="16440" firstSheet="1" activeTab="1" xr2:uid="{A95DC0BB-2293-4BB2-9652-B6AD234FE081}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" firstSheet="2" activeTab="6" xr2:uid="{A95DC0BB-2293-4BB2-9652-B6AD234FE081}"/>
   </bookViews>
   <sheets>
     <sheet name="Description" sheetId="15" r:id="rId1"/>
@@ -583,19 +583,19 @@
     <t>Alternative structure 3</t>
   </si>
   <si>
-    <t>Product 1</t>
-  </si>
-  <si>
-    <t>Product 2</t>
-  </si>
-  <si>
-    <t>Product 1_SMILES</t>
-  </si>
-  <si>
-    <t>Product 2_SMILES</t>
-  </si>
-  <si>
     <t>Transformation Description</t>
+  </si>
+  <si>
+    <t>Product_1</t>
+  </si>
+  <si>
+    <t>Product_1_SMILES</t>
+  </si>
+  <si>
+    <t>Product_2</t>
+  </si>
+  <si>
+    <t>Product_2_SMILES</t>
   </si>
 </sst>
 </file>
@@ -2210,22 +2210,22 @@
         <v>19</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>162</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>35</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="I1" s="5" t="s">
         <v>38</v>

--- a/BART_AUTHOR_YEAR_PathwayName_Template.xlsx
+++ b/BART_AUTHOR_YEAR_PathwayName_Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\strich\Documents\BART\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66A08681-E967-4051-A82D-8A7A686EC45D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A6B2E6F-620E-4F6A-BD4F-AD4D1F3F1C3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" firstSheet="2" activeTab="6" xr2:uid="{A95DC0BB-2293-4BB2-9652-B6AD234FE081}"/>
+    <workbookView xWindow="-28920" yWindow="1605" windowWidth="29040" windowHeight="16440" activeTab="6" xr2:uid="{A95DC0BB-2293-4BB2-9652-B6AD234FE081}"/>
   </bookViews>
   <sheets>
     <sheet name="Description" sheetId="15" r:id="rId1"/>
@@ -101,7 +101,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="769" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="798" uniqueCount="163">
   <si>
     <t>pH</t>
   </si>
@@ -514,9 +514,6 @@
     <t>Experimental Conditions</t>
   </si>
   <si>
-    <t>Phosphorous Content</t>
-  </si>
-  <si>
     <t>Compound Addition</t>
   </si>
   <si>
@@ -557,9 +554,6 @@
   </si>
   <si>
     <t>Sediment</t>
-  </si>
-  <si>
-    <t>Reference: DOI</t>
   </si>
   <si>
     <t>Test General Scenario</t>
@@ -1979,14 +1973,16 @@
       <c r="A3" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="B3" s="18"/>
+      <c r="B3" s="18" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
         <v>56</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -2023,7 +2019,7 @@
   <sheetPr>
     <tabColor rgb="FFC00000"/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.21875" customWidth="1"/>
@@ -2045,13 +2041,13 @@
         <v>5</v>
       </c>
       <c r="D1" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="F1" s="5" t="s">
         <v>157</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -2163,13 +2159,167 @@
       <c r="B18" s="1"/>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>11</v>
+      </c>
       <c r="B19" s="1"/>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>11</v>
+      </c>
       <c r="B20" s="1"/>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>11</v>
+      </c>
       <c r="B21" s="1"/>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>11</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
@@ -2187,7 +2337,7 @@
   <sheetPr>
     <tabColor rgb="FFC00000"/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.77734375" customWidth="1"/>
@@ -2210,22 +2360,22 @@
         <v>19</v>
       </c>
       <c r="C1" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>162</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>164</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>35</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I1" s="5" t="s">
         <v>38</v>
@@ -2234,17 +2384,17 @@
     <row r="2" spans="1:9" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="10"/>
       <c r="B2">
-        <f>_xlfn.XLOOKUP(A2,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(A2,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="C2" s="10"/>
       <c r="D2">
-        <f>_xlfn.XLOOKUP(C2,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(C2,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="E2" s="10"/>
       <c r="F2">
-        <f>_xlfn.XLOOKUP(E2,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(E2,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="G2" s="10"/>
@@ -2252,17 +2402,17 @@
     <row r="3" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="10"/>
       <c r="B3">
-        <f>_xlfn.XLOOKUP(A3,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(A3,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="C3" s="10"/>
       <c r="D3">
-        <f>_xlfn.XLOOKUP(C3,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(C3,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="E3" s="10"/>
       <c r="F3">
-        <f>_xlfn.XLOOKUP(E3,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(E3,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="G3" s="10"/>
@@ -2270,17 +2420,17 @@
     <row r="4" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="10"/>
       <c r="B4">
-        <f>_xlfn.XLOOKUP(A4,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(A4,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="C4" s="10"/>
       <c r="D4">
-        <f>_xlfn.XLOOKUP(C4,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(C4,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="E4" s="10"/>
       <c r="F4">
-        <f>_xlfn.XLOOKUP(E4,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(E4,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="G4" s="10"/>
@@ -2288,17 +2438,17 @@
     <row r="5" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="10"/>
       <c r="B5">
-        <f>_xlfn.XLOOKUP(A5,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(A5,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="C5" s="10"/>
       <c r="D5">
-        <f>_xlfn.XLOOKUP(C5,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(C5,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="E5" s="10"/>
       <c r="F5">
-        <f>_xlfn.XLOOKUP(E5,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(E5,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="G5" s="10"/>
@@ -2306,17 +2456,17 @@
     <row r="6" spans="1:9" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="9"/>
       <c r="B6">
-        <f>_xlfn.XLOOKUP(A6,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(A6,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="C6" s="9"/>
       <c r="D6">
-        <f>_xlfn.XLOOKUP(C6,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(C6,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="E6" s="9"/>
       <c r="F6">
-        <f>_xlfn.XLOOKUP(E6,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(E6,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="G6" s="10"/>
@@ -2324,17 +2474,17 @@
     <row r="7" spans="1:9" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="9"/>
       <c r="B7">
-        <f>_xlfn.XLOOKUP(A7,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(A7,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="C7" s="9"/>
       <c r="D7">
-        <f>_xlfn.XLOOKUP(C7,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(C7,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="E7" s="9"/>
       <c r="F7">
-        <f>_xlfn.XLOOKUP(E7,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(E7,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="G7" s="10"/>
@@ -2342,17 +2492,17 @@
     <row r="8" spans="1:9" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="9"/>
       <c r="B8">
-        <f>_xlfn.XLOOKUP(A8,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(A8,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="C8" s="9"/>
       <c r="D8">
-        <f>_xlfn.XLOOKUP(C8,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(C8,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="E8" s="9"/>
       <c r="F8">
-        <f>_xlfn.XLOOKUP(E8,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(E8,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="G8" s="10"/>
@@ -2360,17 +2510,17 @@
     <row r="9" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="10"/>
       <c r="B9">
-        <f>_xlfn.XLOOKUP(A9,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(A9,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="C9" s="10"/>
       <c r="D9">
-        <f>_xlfn.XLOOKUP(C9,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(C9,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="E9" s="10"/>
       <c r="F9">
-        <f>_xlfn.XLOOKUP(E9,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(E9,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="G9" s="10"/>
@@ -2378,17 +2528,17 @@
     <row r="10" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="10"/>
       <c r="B10">
-        <f>_xlfn.XLOOKUP(A10,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(A10,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="C10" s="10"/>
       <c r="D10">
-        <f>_xlfn.XLOOKUP(C10,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(C10,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="E10" s="10"/>
       <c r="F10">
-        <f>_xlfn.XLOOKUP(E10,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(E10,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="G10" s="10"/>
@@ -2396,17 +2546,17 @@
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="9"/>
       <c r="B11">
-        <f>_xlfn.XLOOKUP(A11,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(A11,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11">
-        <f>_xlfn.XLOOKUP(C11,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(C11,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="E11" s="9"/>
       <c r="F11">
-        <f>_xlfn.XLOOKUP(E11,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(E11,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="G11" s="10"/>
@@ -2414,17 +2564,17 @@
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="9"/>
       <c r="B12">
-        <f>_xlfn.XLOOKUP(A12,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(A12,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="C12" s="9"/>
       <c r="D12">
-        <f>_xlfn.XLOOKUP(C12,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(C12,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="E12" s="9"/>
       <c r="F12">
-        <f>_xlfn.XLOOKUP(E12,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(E12,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="G12" s="10"/>
@@ -2432,17 +2582,17 @@
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="9"/>
       <c r="B13">
-        <f>_xlfn.XLOOKUP(A13,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(A13,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13">
-        <f>_xlfn.XLOOKUP(C13,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(C13,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="E13" s="9"/>
       <c r="F13">
-        <f>_xlfn.XLOOKUP(E13,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(E13,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="G13" s="10"/>
@@ -2450,17 +2600,17 @@
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="9"/>
       <c r="B14">
-        <f>_xlfn.XLOOKUP(A14,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(A14,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14">
-        <f>_xlfn.XLOOKUP(C14,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(C14,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="E14" s="9"/>
       <c r="F14">
-        <f>_xlfn.XLOOKUP(E14,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(E14,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="G14" s="10"/>
@@ -2468,17 +2618,17 @@
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="9"/>
       <c r="B15">
-        <f>_xlfn.XLOOKUP(A15,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(A15,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15">
-        <f>_xlfn.XLOOKUP(C15,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(C15,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="E15" s="9"/>
       <c r="F15">
-        <f>_xlfn.XLOOKUP(E15,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(E15,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="G15" s="10"/>
@@ -2486,17 +2636,17 @@
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="9"/>
       <c r="B16">
-        <f>_xlfn.XLOOKUP(A16,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(A16,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="C16" s="9"/>
       <c r="D16">
-        <f>_xlfn.XLOOKUP(C16,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(C16,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="E16" s="9"/>
       <c r="F16">
-        <f>_xlfn.XLOOKUP(E16,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(E16,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="G16" s="10"/>
@@ -2504,17 +2654,17 @@
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="9"/>
       <c r="B17">
-        <f>_xlfn.XLOOKUP(A17,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(A17,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17">
-        <f>_xlfn.XLOOKUP(C17,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(C17,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="E17" s="9"/>
       <c r="F17">
-        <f>_xlfn.XLOOKUP(E17,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(E17,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="G17" s="10"/>
@@ -2522,17 +2672,17 @@
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="9"/>
       <c r="B18">
-        <f>_xlfn.XLOOKUP(A18,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(A18,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="C18" s="9"/>
       <c r="D18">
-        <f>_xlfn.XLOOKUP(C18,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(C18,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="E18" s="9"/>
       <c r="F18">
-        <f>_xlfn.XLOOKUP(E18,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(E18,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="G18" s="10"/>
@@ -2540,17 +2690,17 @@
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="9"/>
       <c r="B19">
-        <f>_xlfn.XLOOKUP(A19,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(A19,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19">
-        <f>_xlfn.XLOOKUP(C19,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(C19,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="E19" s="9"/>
       <c r="F19">
-        <f>_xlfn.XLOOKUP(E19,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(E19,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="G19" s="10"/>
@@ -2558,17 +2708,17 @@
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="9"/>
       <c r="B20">
-        <f>_xlfn.XLOOKUP(A20,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(A20,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="C20" s="9"/>
       <c r="D20">
-        <f>_xlfn.XLOOKUP(C20,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(C20,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="E20" s="9"/>
       <c r="F20">
-        <f>_xlfn.XLOOKUP(E20,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(E20,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="G20" s="10"/>
@@ -2576,17 +2726,17 @@
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="9"/>
       <c r="B21">
-        <f>_xlfn.XLOOKUP(A21,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(A21,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21">
-        <f>_xlfn.XLOOKUP(C21,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(C21,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="E21" s="9"/>
       <c r="F21">
-        <f>_xlfn.XLOOKUP(E21,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(E21,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="G21" s="10"/>
@@ -2594,17 +2744,17 @@
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="9"/>
       <c r="B22">
-        <f>_xlfn.XLOOKUP(A22,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(A22,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="C22" s="9"/>
       <c r="D22">
-        <f>_xlfn.XLOOKUP(C22,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(C22,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="E22" s="9"/>
       <c r="F22">
-        <f>_xlfn.XLOOKUP(E22,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(E22,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="G22" s="10"/>
@@ -2612,43 +2762,511 @@
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="9"/>
       <c r="B23">
-        <f>_xlfn.XLOOKUP(A23,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(A23,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23">
-        <f>_xlfn.XLOOKUP(C23,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(C23,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="E23" s="9"/>
       <c r="F23">
-        <f>_xlfn.XLOOKUP(E23,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(E23,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="G23" s="10"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="9"/>
+      <c r="B24">
+        <f>_xlfn.XLOOKUP(A24,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
       <c r="C24" s="9"/>
+      <c r="D24">
+        <f>_xlfn.XLOOKUP(C24,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
       <c r="E24" s="9"/>
+      <c r="F24">
+        <f>_xlfn.XLOOKUP(E24,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
       <c r="G24" s="10"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="9"/>
+      <c r="B25">
+        <f>_xlfn.XLOOKUP(A25,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
       <c r="C25" s="9"/>
+      <c r="D25">
+        <f>_xlfn.XLOOKUP(C25,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
       <c r="E25" s="9"/>
+      <c r="F25">
+        <f>_xlfn.XLOOKUP(E25,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
       <c r="G25" s="10"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="9"/>
+      <c r="B26">
+        <f>_xlfn.XLOOKUP(A26,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
       <c r="C26" s="9"/>
+      <c r="D26">
+        <f>_xlfn.XLOOKUP(C26,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
       <c r="E26" s="9"/>
+      <c r="F26">
+        <f>_xlfn.XLOOKUP(E26,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
       <c r="G26" s="10"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="10"/>
+      <c r="B27">
+        <f>_xlfn.XLOOKUP(A27,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="C27" s="10"/>
+      <c r="D27">
+        <f>_xlfn.XLOOKUP(C27,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="E27" s="10"/>
+      <c r="F27">
+        <f>_xlfn.XLOOKUP(E27,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="G27" s="10"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" s="10"/>
+      <c r="B28">
+        <f>_xlfn.XLOOKUP(A28,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="C28" s="10"/>
+      <c r="D28">
+        <f>_xlfn.XLOOKUP(C28,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="E28" s="10"/>
+      <c r="F28">
+        <f>_xlfn.XLOOKUP(E28,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="G28" s="10"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" s="9"/>
+      <c r="B29">
+        <f>_xlfn.XLOOKUP(A29,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="C29" s="10"/>
+      <c r="D29">
+        <f>_xlfn.XLOOKUP(C29,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="E29" s="10"/>
+      <c r="F29">
+        <f>_xlfn.XLOOKUP(E29,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="G29" s="10"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" s="9"/>
+      <c r="B30">
+        <f>_xlfn.XLOOKUP(A30,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="C30" s="10"/>
+      <c r="D30">
+        <f>_xlfn.XLOOKUP(C30,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="E30" s="10"/>
+      <c r="F30">
+        <f>_xlfn.XLOOKUP(E30,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="G30" s="10"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" s="9"/>
+      <c r="B31">
+        <f>_xlfn.XLOOKUP(A31,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="C31" s="9"/>
+      <c r="D31">
+        <f>_xlfn.XLOOKUP(C31,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="E31" s="9"/>
+      <c r="F31">
+        <f>_xlfn.XLOOKUP(E31,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="G31" s="10"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" s="9"/>
+      <c r="B32">
+        <f>_xlfn.XLOOKUP(A32,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="C32" s="9"/>
+      <c r="D32">
+        <f>_xlfn.XLOOKUP(C32,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="E32" s="9"/>
+      <c r="F32">
+        <f>_xlfn.XLOOKUP(E32,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="G32" s="10"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" s="9"/>
+      <c r="B33">
+        <f>_xlfn.XLOOKUP(A33,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="C33" s="9"/>
+      <c r="D33">
+        <f>_xlfn.XLOOKUP(C33,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="E33" s="9"/>
+      <c r="F33">
+        <f>_xlfn.XLOOKUP(E33,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="G33" s="10"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34" s="9"/>
+      <c r="B34">
+        <f>_xlfn.XLOOKUP(A34,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="C34" s="10"/>
+      <c r="D34">
+        <f>_xlfn.XLOOKUP(C34,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="E34" s="10"/>
+      <c r="F34">
+        <f>_xlfn.XLOOKUP(E34,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="G34" s="10"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" s="9"/>
+      <c r="B35">
+        <f>_xlfn.XLOOKUP(A35,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="C35" s="10"/>
+      <c r="D35">
+        <f>_xlfn.XLOOKUP(C35,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="E35" s="10"/>
+      <c r="F35">
+        <f>_xlfn.XLOOKUP(E35,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="G35" s="10"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A36" s="9"/>
+      <c r="B36">
+        <f>_xlfn.XLOOKUP(A36,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="C36" s="9"/>
+      <c r="D36">
+        <f>_xlfn.XLOOKUP(C36,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="E36" s="9"/>
+      <c r="F36">
+        <f>_xlfn.XLOOKUP(E36,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="G36" s="10"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A37" s="9"/>
+      <c r="B37">
+        <f>_xlfn.XLOOKUP(A37,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="C37" s="9"/>
+      <c r="D37">
+        <f>_xlfn.XLOOKUP(C37,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="E37" s="9"/>
+      <c r="F37">
+        <f>_xlfn.XLOOKUP(E37,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="G37" s="10"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38" s="9"/>
+      <c r="B38">
+        <f>_xlfn.XLOOKUP(A38,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="C38" s="9"/>
+      <c r="D38">
+        <f>_xlfn.XLOOKUP(C38,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="E38" s="9"/>
+      <c r="F38">
+        <f>_xlfn.XLOOKUP(E38,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="G38" s="10"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39" s="9"/>
+      <c r="B39">
+        <f>_xlfn.XLOOKUP(A39,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="C39" s="9"/>
+      <c r="D39">
+        <f>_xlfn.XLOOKUP(C39,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="E39" s="9"/>
+      <c r="F39">
+        <f>_xlfn.XLOOKUP(E39,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="G39" s="10"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A40" s="9"/>
+      <c r="B40">
+        <f>_xlfn.XLOOKUP(A40,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="C40" s="9"/>
+      <c r="D40">
+        <f>_xlfn.XLOOKUP(C40,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="E40" s="9"/>
+      <c r="F40">
+        <f>_xlfn.XLOOKUP(E40,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="G40" s="10"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A41" s="9"/>
+      <c r="B41">
+        <f>_xlfn.XLOOKUP(A41,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="C41" s="9"/>
+      <c r="D41">
+        <f>_xlfn.XLOOKUP(C41,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="E41" s="9"/>
+      <c r="F41">
+        <f>_xlfn.XLOOKUP(E41,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="G41" s="10"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A42" s="9"/>
+      <c r="B42">
+        <f>_xlfn.XLOOKUP(A42,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="C42" s="9"/>
+      <c r="D42">
+        <f>_xlfn.XLOOKUP(C42,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="E42" s="9"/>
+      <c r="F42">
+        <f>_xlfn.XLOOKUP(E42,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="G42" s="10"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A43" s="9"/>
+      <c r="B43">
+        <f>_xlfn.XLOOKUP(A43,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="C43" s="9"/>
+      <c r="D43">
+        <f>_xlfn.XLOOKUP(C43,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="E43" s="9"/>
+      <c r="F43">
+        <f>_xlfn.XLOOKUP(E43,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="G43" s="10"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A44" s="9"/>
+      <c r="B44">
+        <f>_xlfn.XLOOKUP(A44,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="C44" s="9"/>
+      <c r="D44">
+        <f>_xlfn.XLOOKUP(C44,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="E44" s="9"/>
+      <c r="F44">
+        <f>_xlfn.XLOOKUP(E44,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="G44" s="10"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A45" s="9"/>
+      <c r="B45">
+        <f>_xlfn.XLOOKUP(A45,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="C45" s="9"/>
+      <c r="D45">
+        <f>_xlfn.XLOOKUP(C45,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="E45" s="9"/>
+      <c r="F45">
+        <f>_xlfn.XLOOKUP(E45,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="G45" s="10"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A46" s="9"/>
+      <c r="B46">
+        <f>_xlfn.XLOOKUP(A46,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="C46" s="9"/>
+      <c r="D46">
+        <f>_xlfn.XLOOKUP(C46,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="E46" s="9"/>
+      <c r="F46">
+        <f>_xlfn.XLOOKUP(E46,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="G46" s="10"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A47" s="9"/>
+      <c r="B47">
+        <f>_xlfn.XLOOKUP(A47,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="C47" s="9"/>
+      <c r="D47">
+        <f>_xlfn.XLOOKUP(C47,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="E47" s="9"/>
+      <c r="F47">
+        <f>_xlfn.XLOOKUP(E47,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="G47" s="10"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A48" s="9"/>
+      <c r="B48">
+        <f>_xlfn.XLOOKUP(A48,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="C48" s="9"/>
+      <c r="D48">
+        <f>_xlfn.XLOOKUP(C48,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="E48" s="9"/>
+      <c r="F48">
+        <f>_xlfn.XLOOKUP(E48,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="G48" s="10"/>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="9"/>
+      <c r="B49">
+        <f>_xlfn.XLOOKUP(A49,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="C49" s="9"/>
+      <c r="D49">
+        <f>_xlfn.XLOOKUP(C49,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="E49" s="9"/>
+      <c r="F49">
+        <f>_xlfn.XLOOKUP(E49,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="G49" s="10"/>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="9"/>
+      <c r="B50">
+        <f>_xlfn.XLOOKUP(A50,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="C50" s="9"/>
+      <c r="D50">
+        <f>_xlfn.XLOOKUP(C50,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="E50" s="9"/>
+      <c r="F50">
+        <f>_xlfn.XLOOKUP(E50,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="G50" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G26" xr:uid="{4E4B432C-3A87-4B1A-A0B5-DE103EF115B8}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G50" xr:uid="{4E4B432C-3A87-4B1A-A0B5-DE103EF115B8}">
       <formula1>"multistep reaction, "</formula1>
     </dataValidation>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Multistep" prompt="If the reported reaction consisted of multiple enzymatic steps, please note this here by choosing &quot;multistep reaction&quot;" sqref="G1" xr:uid="{670B067C-E023-4CDC-B74A-A2B35314F74C}"/>
@@ -2663,7 +3281,7 @@
           <x14:formula1>
             <xm:f>Compounds!$B$2:$B$21</xm:f>
           </x14:formula1>
-          <xm:sqref>C2:C26 A2:A26 E2:E26</xm:sqref>
+          <xm:sqref>C2:C50 A2:A50 E2:E50</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2726,7 +3344,7 @@
         <v>9</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C2" s="55" t="s">
         <v>135</v>
@@ -2744,8 +3362,9 @@
       <c r="A3" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="7" t="s">
-        <v>152</v>
+      <c r="B3" s="7" t="str">
+        <f>"Reference: " &amp;Description!B3</f>
+        <v>Reference: DOI</v>
       </c>
       <c r="C3" s="56"/>
       <c r="D3" s="26" t="s">
@@ -3128,7 +3747,7 @@
     <row r="30" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C30" s="56"/>
       <c r="D30" s="26" t="s">
-        <v>137</v>
+        <v>33</v>
       </c>
       <c r="E30" s="27"/>
       <c r="F30" s="28"/>
@@ -3143,7 +3762,7 @@
     <row r="31" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C31" s="56"/>
       <c r="D31" s="26" t="s">
-        <v>137</v>
+        <v>33</v>
       </c>
       <c r="E31" s="27"/>
       <c r="F31" s="28"/>
@@ -3269,7 +3888,7 @@
     </row>
     <row r="40" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C40" s="55" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D40" s="39" t="s">
         <v>23</v>
@@ -3334,7 +3953,7 @@
     </row>
     <row r="45" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C45" s="55" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D45" s="39" t="s">
         <v>76</v>
@@ -3544,7 +4163,7 @@
         <v>49</v>
       </c>
       <c r="C1" s="46" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D1" s="47" t="s">
         <v>2</v>
@@ -3570,10 +4189,10 @@
         <v>9</v>
       </c>
       <c r="B2" s="38" t="s">
+        <v>140</v>
+      </c>
+      <c r="C2" s="55" t="s">
         <v>141</v>
-      </c>
-      <c r="C2" s="55" t="s">
-        <v>142</v>
       </c>
       <c r="D2" s="39" t="s">
         <v>117</v>
@@ -3588,8 +4207,9 @@
       <c r="A3" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="38" t="s">
-        <v>152</v>
+      <c r="B3" s="38" t="str">
+        <f>"Reference: " &amp;Description!B3</f>
+        <v>Reference: DOI</v>
       </c>
       <c r="C3" s="56"/>
       <c r="D3" s="26" t="s">
@@ -3659,7 +4279,7 @@
     </row>
     <row r="8" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C8" s="55" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D8" s="39" t="s">
         <v>1</v>
@@ -3920,7 +4540,7 @@
     </row>
     <row r="26" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C26" s="55" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D26" s="39" t="s">
         <v>127</v>
@@ -3946,7 +4566,7 @@
     </row>
     <row r="28" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C28" s="55" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D28" s="39" t="s">
         <v>76</v>
@@ -4061,7 +4681,7 @@
       </c>
       <c r="E36" s="34"/>
       <c r="F36" s="35" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G36" s="34"/>
       <c r="H36" s="45"/>
@@ -4138,7 +4758,7 @@
         <v>49</v>
       </c>
       <c r="C1" s="46" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D1" s="47" t="s">
         <v>2</v>
@@ -4164,10 +4784,10 @@
         <v>9</v>
       </c>
       <c r="B2" s="38" t="s">
+        <v>146</v>
+      </c>
+      <c r="C2" s="55" t="s">
         <v>147</v>
-      </c>
-      <c r="C2" s="55" t="s">
-        <v>148</v>
       </c>
       <c r="D2" s="39" t="s">
         <v>114</v>
@@ -4182,8 +4802,9 @@
       <c r="A3" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="38" t="s">
-        <v>152</v>
+      <c r="B3" s="38" t="str">
+        <f>"Reference: " &amp;Description!B3</f>
+        <v>Reference: DOI</v>
       </c>
       <c r="C3" s="56"/>
       <c r="D3" s="26" t="s">
@@ -4305,7 +4926,7 @@
     </row>
     <row r="12" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C12" s="55" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D12" s="39" t="s">
         <v>69</v>
@@ -4885,7 +5506,7 @@
         <v>81</v>
       </c>
       <c r="E48" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F48" s="28"/>
       <c r="G48" t="s">
@@ -4900,7 +5521,7 @@
         <v>81</v>
       </c>
       <c r="E49" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F49" s="28"/>
       <c r="G49" t="s">
@@ -4924,7 +5545,7 @@
     </row>
     <row r="51" spans="3:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C51" s="58" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D51" s="39" t="s">
         <v>127</v>
@@ -4950,7 +5571,7 @@
     </row>
     <row r="53" spans="3:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C53" s="55" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D53" s="39" t="s">
         <v>76</v>
@@ -5065,7 +5686,7 @@
       </c>
       <c r="E61" s="34"/>
       <c r="F61" s="35" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G61" s="34"/>
       <c r="H61" s="45"/>
@@ -5157,7 +5778,7 @@
         <v>9</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C2" s="26" t="s">
         <v>12</v>
@@ -5172,8 +5793,9 @@
       <c r="A3" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="38" t="s">
-        <v>152</v>
+      <c r="B3" s="38" t="str">
+        <f>"Reference: " &amp;Description!B3</f>
+        <v>Reference: DOI</v>
       </c>
       <c r="C3" s="26" t="s">
         <v>61</v>
@@ -6514,7 +7136,7 @@
       </c>
       <c r="D103" s="34"/>
       <c r="E103" s="35" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F103" s="34"/>
       <c r="G103" s="34"/>
@@ -6589,7 +7211,7 @@
   <sheetPr>
     <tabColor rgb="FFC00000"/>
   </sheetPr>
-  <dimension ref="A1:M49"/>
+  <dimension ref="A1:M50"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27.109375" customWidth="1"/>
@@ -6651,7 +7273,7 @@
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B2" s="10"/>
       <c r="C2">
-        <f>_xlfn.XLOOKUP(B2,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(B2,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="E2" s="10"/>
@@ -6663,7 +7285,7 @@
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B3" s="10"/>
       <c r="C3">
-        <f>_xlfn.XLOOKUP(B3,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(B3,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="E3" s="10"/>
@@ -6675,7 +7297,7 @@
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B4" s="10"/>
       <c r="C4">
-        <f>_xlfn.XLOOKUP(B4,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(B4,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="E4" s="10"/>
@@ -6687,7 +7309,7 @@
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B5" s="10"/>
       <c r="C5">
-        <f>_xlfn.XLOOKUP(B5,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(B5,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="E5" s="10"/>
@@ -6699,7 +7321,7 @@
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B6" s="10"/>
       <c r="C6">
-        <f>_xlfn.XLOOKUP(B6,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(B6,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="E6" s="10"/>
@@ -6711,7 +7333,7 @@
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B7" s="10"/>
       <c r="C7">
-        <f>_xlfn.XLOOKUP(B7,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(B7,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="E7" s="10"/>
@@ -6723,7 +7345,7 @@
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B8" s="9"/>
       <c r="C8">
-        <f>_xlfn.XLOOKUP(B8,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(B8,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="E8" s="10"/>
@@ -6736,7 +7358,7 @@
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B9" s="9"/>
       <c r="C9">
-        <f>_xlfn.XLOOKUP(B9,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(B9,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="E9" s="10"/>
@@ -6749,7 +7371,7 @@
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B10" s="10"/>
       <c r="C10">
-        <f>_xlfn.XLOOKUP(B10,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(B10,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="E10" s="10"/>
@@ -6763,7 +7385,7 @@
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B11" s="10"/>
       <c r="C11">
-        <f>_xlfn.XLOOKUP(B11,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(B11,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="E11" s="10"/>
@@ -6777,7 +7399,7 @@
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B12" s="10"/>
       <c r="C12">
-        <f>_xlfn.XLOOKUP(B12,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(B12,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="E12" s="10"/>
@@ -6791,7 +7413,7 @@
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B13" s="10"/>
       <c r="C13">
-        <f>_xlfn.XLOOKUP(B13,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(B13,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="E13" s="10"/>
@@ -6805,7 +7427,7 @@
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B14" s="10"/>
       <c r="C14">
-        <f>_xlfn.XLOOKUP(B14,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(B14,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="E14" s="10"/>
@@ -6819,7 +7441,7 @@
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B15" s="9"/>
       <c r="C15">
-        <f>_xlfn.XLOOKUP(B15,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(B15,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="E15" s="10"/>
@@ -6833,7 +7455,7 @@
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B16" s="9"/>
       <c r="C16">
-        <f>_xlfn.XLOOKUP(B16,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(B16,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="E16" s="10"/>
@@ -6847,7 +7469,7 @@
     <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B17" s="9"/>
       <c r="C17">
-        <f>_xlfn.XLOOKUP(B17,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(B17,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="E17" s="10"/>
@@ -6861,7 +7483,7 @@
     <row r="18" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B18" s="9"/>
       <c r="C18">
-        <f>_xlfn.XLOOKUP(B18,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(B18,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
         <v>0</v>
       </c>
       <c r="E18" s="10"/>
@@ -6874,6 +7496,10 @@
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B19" s="9"/>
+      <c r="C19">
+        <f>_xlfn.XLOOKUP(B19,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
       <c r="E19" s="10"/>
       <c r="G19" s="10"/>
       <c r="H19" s="11"/>
@@ -6884,6 +7510,10 @@
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B20" s="9"/>
+      <c r="C20">
+        <f>_xlfn.XLOOKUP(B20,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
       <c r="E20" s="10"/>
       <c r="G20" s="10"/>
       <c r="H20" s="11"/>
@@ -6894,6 +7524,10 @@
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B21" s="10"/>
+      <c r="C21">
+        <f>_xlfn.XLOOKUP(B21,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
       <c r="E21" s="10"/>
       <c r="G21" s="10"/>
       <c r="H21" s="11"/>
@@ -6904,6 +7538,10 @@
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B22" s="9"/>
+      <c r="C22">
+        <f>_xlfn.XLOOKUP(B22,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
       <c r="E22" s="10"/>
       <c r="G22" s="10"/>
       <c r="H22" s="11"/>
@@ -6914,6 +7552,10 @@
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B23" s="9"/>
+      <c r="C23">
+        <f>_xlfn.XLOOKUP(B23,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
       <c r="E23" s="10"/>
       <c r="G23" s="10"/>
       <c r="H23" s="11"/>
@@ -6924,6 +7566,10 @@
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B24" s="9"/>
+      <c r="C24">
+        <f>_xlfn.XLOOKUP(B24,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
       <c r="E24" s="10"/>
       <c r="G24" s="10"/>
       <c r="H24" s="11"/>
@@ -6934,6 +7580,10 @@
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B25" s="9"/>
+      <c r="C25">
+        <f>_xlfn.XLOOKUP(B25,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
       <c r="E25" s="10"/>
       <c r="G25" s="10"/>
       <c r="H25" s="11"/>
@@ -6942,84 +7592,371 @@
       <c r="K25" s="3"/>
       <c r="L25" s="11"/>
     </row>
+    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B26" s="9"/>
+      <c r="C26">
+        <f>_xlfn.XLOOKUP(B26,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="E26" s="10"/>
+      <c r="G26" s="10"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="3"/>
+      <c r="J26" s="3"/>
+      <c r="K26" s="3"/>
+      <c r="L26" s="11"/>
+    </row>
+    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B27" s="9"/>
+      <c r="C27">
+        <f>_xlfn.XLOOKUP(B27,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="E27" s="10"/>
+      <c r="G27" s="10"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="3"/>
+      <c r="J27" s="3"/>
+      <c r="K27" s="3"/>
+      <c r="L27" s="11"/>
+    </row>
+    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B28" s="9"/>
+      <c r="C28">
+        <f>_xlfn.XLOOKUP(B28,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="E28" s="10"/>
+      <c r="G28" s="10"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="3"/>
+      <c r="J28" s="3"/>
+      <c r="K28" s="3"/>
+      <c r="L28" s="11"/>
+    </row>
+    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B29" s="9"/>
+      <c r="C29">
+        <f>_xlfn.XLOOKUP(B29,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="E29" s="10"/>
+      <c r="G29" s="10"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="3"/>
+      <c r="J29" s="3"/>
+      <c r="K29" s="3"/>
+      <c r="L29" s="11"/>
+    </row>
+    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B30" s="9"/>
+      <c r="C30">
+        <f>_xlfn.XLOOKUP(B30,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="E30" s="10"/>
+      <c r="G30" s="10"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="3"/>
+      <c r="J30" s="3"/>
+      <c r="K30" s="3"/>
+      <c r="L30" s="11"/>
+    </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="G31" s="3"/>
-      <c r="H31" s="3"/>
+      <c r="B31" s="10"/>
+      <c r="C31">
+        <f>_xlfn.XLOOKUP(B31,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="E31" s="10"/>
+      <c r="G31" s="10"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="3"/>
+      <c r="J31" s="3"/>
+      <c r="K31" s="3"/>
+      <c r="L31" s="11"/>
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B32" s="1"/>
-      <c r="G32" s="3"/>
-      <c r="H32" s="3"/>
-    </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B33" s="1"/>
-      <c r="G33" s="3"/>
-      <c r="H33" s="3"/>
-    </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B34" s="1"/>
-    </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B35" s="1"/>
-    </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B36" s="1"/>
-    </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B37" s="1"/>
-    </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B38" s="1"/>
-    </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B39" s="1"/>
-    </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B40" s="1"/>
-    </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B41" s="1"/>
-    </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B42" s="1"/>
-    </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B43" s="1"/>
-    </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B44" s="1"/>
-    </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B45" s="1"/>
-    </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B46" s="1"/>
-    </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B47" s="1"/>
-    </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B48" s="1"/>
-    </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B49" s="1"/>
+      <c r="B32" s="9"/>
+      <c r="C32">
+        <f>_xlfn.XLOOKUP(B32,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="E32" s="10"/>
+      <c r="G32" s="10"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="3"/>
+      <c r="J32" s="3"/>
+      <c r="K32" s="3"/>
+      <c r="L32" s="11"/>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B33" s="9"/>
+      <c r="C33">
+        <f>_xlfn.XLOOKUP(B33,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="E33" s="10"/>
+      <c r="G33" s="10"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="3"/>
+      <c r="J33" s="3"/>
+      <c r="K33" s="3"/>
+      <c r="L33" s="11"/>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B34" s="9"/>
+      <c r="C34">
+        <f>_xlfn.XLOOKUP(B34,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="E34" s="10"/>
+      <c r="G34" s="10"/>
+      <c r="H34" s="11"/>
+      <c r="I34" s="3"/>
+      <c r="J34" s="3"/>
+      <c r="K34" s="3"/>
+      <c r="L34" s="11"/>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B35" s="9"/>
+      <c r="C35">
+        <f>_xlfn.XLOOKUP(B35,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="E35" s="10"/>
+      <c r="G35" s="10"/>
+      <c r="H35" s="11"/>
+      <c r="I35" s="3"/>
+      <c r="J35" s="3"/>
+      <c r="K35" s="3"/>
+      <c r="L35" s="11"/>
+    </row>
+    <row r="36" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B36" s="9"/>
+      <c r="C36">
+        <f>_xlfn.XLOOKUP(B36,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="E36" s="10"/>
+      <c r="G36" s="10"/>
+      <c r="H36" s="11"/>
+      <c r="I36" s="3"/>
+      <c r="J36" s="3"/>
+      <c r="K36" s="3"/>
+      <c r="L36" s="11"/>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B37" s="9"/>
+      <c r="C37">
+        <f>_xlfn.XLOOKUP(B37,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="E37" s="10"/>
+      <c r="G37" s="10"/>
+      <c r="H37" s="11"/>
+      <c r="I37" s="3"/>
+      <c r="J37" s="3"/>
+      <c r="K37" s="3"/>
+      <c r="L37" s="11"/>
+    </row>
+    <row r="38" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B38" s="9"/>
+      <c r="C38">
+        <f>_xlfn.XLOOKUP(B38,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="E38" s="10"/>
+      <c r="G38" s="10"/>
+      <c r="H38" s="11"/>
+      <c r="I38" s="3"/>
+      <c r="J38" s="3"/>
+      <c r="K38" s="3"/>
+      <c r="L38" s="11"/>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B39" s="9"/>
+      <c r="C39">
+        <f>_xlfn.XLOOKUP(B39,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="E39" s="10"/>
+      <c r="G39" s="10"/>
+      <c r="H39" s="11"/>
+      <c r="I39" s="3"/>
+      <c r="J39" s="3"/>
+      <c r="K39" s="3"/>
+      <c r="L39" s="11"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B40" s="9"/>
+      <c r="C40">
+        <f>_xlfn.XLOOKUP(B40,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="E40" s="10"/>
+      <c r="G40" s="10"/>
+      <c r="H40" s="11"/>
+      <c r="I40" s="3"/>
+      <c r="J40" s="3"/>
+      <c r="K40" s="3"/>
+      <c r="L40" s="11"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B41" s="10"/>
+      <c r="C41">
+        <f>_xlfn.XLOOKUP(B41,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="E41" s="10"/>
+      <c r="G41" s="10"/>
+      <c r="H41" s="11"/>
+      <c r="I41" s="3"/>
+      <c r="J41" s="3"/>
+      <c r="K41" s="3"/>
+      <c r="L41" s="11"/>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B42" s="9"/>
+      <c r="C42">
+        <f>_xlfn.XLOOKUP(B42,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="E42" s="10"/>
+      <c r="G42" s="10"/>
+      <c r="H42" s="11"/>
+      <c r="I42" s="3"/>
+      <c r="J42" s="3"/>
+      <c r="K42" s="3"/>
+      <c r="L42" s="11"/>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B43" s="9"/>
+      <c r="C43">
+        <f>_xlfn.XLOOKUP(B43,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="E43" s="10"/>
+      <c r="G43" s="10"/>
+      <c r="H43" s="11"/>
+      <c r="I43" s="3"/>
+      <c r="J43" s="3"/>
+      <c r="K43" s="3"/>
+      <c r="L43" s="11"/>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B44" s="9"/>
+      <c r="C44">
+        <f>_xlfn.XLOOKUP(B44,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="E44" s="10"/>
+      <c r="G44" s="10"/>
+      <c r="H44" s="11"/>
+      <c r="I44" s="3"/>
+      <c r="J44" s="3"/>
+      <c r="K44" s="3"/>
+      <c r="L44" s="11"/>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B45" s="9"/>
+      <c r="C45">
+        <f>_xlfn.XLOOKUP(B45,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="E45" s="10"/>
+      <c r="G45" s="10"/>
+      <c r="H45" s="11"/>
+      <c r="I45" s="3"/>
+      <c r="J45" s="3"/>
+      <c r="K45" s="3"/>
+      <c r="L45" s="11"/>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B46" s="9"/>
+      <c r="C46">
+        <f>_xlfn.XLOOKUP(B46,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="E46" s="10"/>
+      <c r="G46" s="10"/>
+      <c r="H46" s="11"/>
+      <c r="I46" s="3"/>
+      <c r="J46" s="3"/>
+      <c r="K46" s="3"/>
+      <c r="L46" s="11"/>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B47" s="9"/>
+      <c r="C47">
+        <f>_xlfn.XLOOKUP(B47,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="E47" s="10"/>
+      <c r="G47" s="10"/>
+      <c r="H47" s="11"/>
+      <c r="I47" s="3"/>
+      <c r="J47" s="3"/>
+      <c r="K47" s="3"/>
+      <c r="L47" s="11"/>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B48" s="9"/>
+      <c r="C48">
+        <f>_xlfn.XLOOKUP(B48,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="E48" s="10"/>
+      <c r="G48" s="10"/>
+      <c r="H48" s="11"/>
+      <c r="I48" s="3"/>
+      <c r="J48" s="3"/>
+      <c r="K48" s="3"/>
+      <c r="L48" s="11"/>
+    </row>
+    <row r="49" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B49" s="9"/>
+      <c r="C49">
+        <f>_xlfn.XLOOKUP(B49,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="E49" s="10"/>
+      <c r="G49" s="10"/>
+      <c r="H49" s="11"/>
+      <c r="I49" s="3"/>
+      <c r="J49" s="3"/>
+      <c r="K49" s="3"/>
+      <c r="L49" s="11"/>
+    </row>
+    <row r="50" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B50" s="9"/>
+      <c r="C50">
+        <f>_xlfn.XLOOKUP(B50,Compounds!$B$2:$B$50,Compounds!$C$2:$C$50)</f>
+        <v>0</v>
+      </c>
+      <c r="E50" s="10"/>
+      <c r="G50" s="10"/>
+      <c r="H50" s="11"/>
+      <c r="I50" s="3"/>
+      <c r="J50" s="3"/>
+      <c r="K50" s="3"/>
+      <c r="L50" s="11"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
-  <dataValidations count="9">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="B32:C34 B40:B41" xr:uid="{9D9F6508-2F0E-4BCF-9953-79AD6A40D29A}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E25" xr:uid="{930A2329-8F94-46CF-AC1A-5BF5455DF29F}">
+  <dataValidations count="8">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E50" xr:uid="{930A2329-8F94-46CF-AC1A-5BF5455DF29F}">
       <formula1>"Half-life, Rate constant, NA"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H25" xr:uid="{E543FE4B-6E7F-4EA1-B690-255293F334F8}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H50" xr:uid="{E543FE4B-6E7F-4EA1-B690-255293F334F8}">
       <formula1>"sorption corrected, abiotic degradation corrected, sorption corrected &amp; abiotic degradation corrected, NA"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L25" xr:uid="{975F3CE3-4F63-4C16-BA52-2318021B2EC7}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L50" xr:uid="{975F3CE3-4F63-4C16-BA52-2318021B2EC7}">
       <formula1>"proposed, NA"</formula1>
     </dataValidation>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Parameter" prompt="Reported kinetic parameter - either Half-life or Rate constant." sqref="E1" xr:uid="{F18A74F6-59D7-4E6F-8ACE-C49737E375AB}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Model" prompt="Model used to generate the kinetic parameter - i.e. &quot;first-order&quot;" sqref="D1 D4:D9" xr:uid="{F0E7BF00-EF0F-466F-B6C0-D6C929A210D5}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G25" xr:uid="{18FBD4A5-6172-4673-B672-FBAFE09DD58A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G50" xr:uid="{18FBD4A5-6172-4673-B672-FBAFE09DD58A}">
       <formula1>"d, 1/d, NA"</formula1>
     </dataValidation>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Value Unit" prompt="Units for input kinetic parameter - usually d for Half-lives and 1/d for rate constants" sqref="G1" xr:uid="{D3E30F72-B6AE-42D0-9C59-C6C416144E46}"/>
@@ -7033,7 +7970,7 @@
           <x14:formula1>
             <xm:f>Compounds!$B$2:$B$21</xm:f>
           </x14:formula1>
-          <xm:sqref>B2:B25</xm:sqref>
+          <xm:sqref>B2:B50</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
